--- a/META.xlsx
+++ b/META.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" state="visible" r:id="rId3"/>
@@ -383,7 +383,7 @@
                 <xdr:col>26</xdr:col>
                 <xdr:colOff>1</xdr:colOff>
                 <xdr:row>110</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:rowOff>1</xdr:rowOff>
               </xdr:from>
               <xdr:to>
                 <xdr:col>27</xdr:col>
@@ -423,7 +423,7 @@
                 <xdr:col>42</xdr:col>
                 <xdr:colOff>1</xdr:colOff>
                 <xdr:row>144</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:rowOff>1</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -436,7 +436,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="612" uniqueCount="363">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="614" uniqueCount="363">
   <si>
     <t xml:space="preserve">META</t>
   </si>
@@ -1067,6 +1067,9 @@
     <t xml:space="preserve">Equity Value</t>
   </si>
   <si>
+    <t xml:space="preserve">Diff</t>
+  </si>
+  <si>
     <t xml:space="preserve">Tax Rate</t>
   </si>
   <si>
@@ -1080,9 +1083,6 @@
   </si>
   <si>
     <t xml:space="preserve">Share</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Diff</t>
   </si>
   <si>
     <t xml:space="preserve">Dividend Yield</t>
@@ -1873,7 +1873,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="92">
+  <cellXfs count="93">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2144,6 +2144,10 @@
     </xf>
     <xf numFmtId="169" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="4" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -3411,11 +3415,11 @@
         </c:ser>
         <c:gapWidth val="100"/>
         <c:overlap val="0"/>
-        <c:axId val="64731116"/>
-        <c:axId val="16507339"/>
+        <c:axId val="81462775"/>
+        <c:axId val="20935485"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="64731116"/>
+        <c:axId val="81462775"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3448,7 +3452,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="16507339"/>
+        <c:crossAx val="20935485"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3456,7 +3460,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="16507339"/>
+        <c:axId val="20935485"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3498,7 +3502,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="64731116"/>
+        <c:crossAx val="81462775"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4622,11 +4626,11 @@
         </c:ser>
         <c:gapWidth val="100"/>
         <c:overlap val="0"/>
-        <c:axId val="62069037"/>
-        <c:axId val="65082582"/>
+        <c:axId val="10987297"/>
+        <c:axId val="66396690"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="62069037"/>
+        <c:axId val="10987297"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4659,7 +4663,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="65082582"/>
+        <c:crossAx val="66396690"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4667,7 +4671,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="65082582"/>
+        <c:axId val="66396690"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4709,7 +4713,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="62069037"/>
+        <c:crossAx val="10987297"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4937,11 +4941,11 @@
         </c:ser>
         <c:gapWidth val="100"/>
         <c:overlap val="0"/>
-        <c:axId val="43057617"/>
-        <c:axId val="33170700"/>
+        <c:axId val="45945190"/>
+        <c:axId val="43810199"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="43057617"/>
+        <c:axId val="45945190"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4974,7 +4978,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="33170700"/>
+        <c:crossAx val="43810199"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4982,7 +4986,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="33170700"/>
+        <c:axId val="43810199"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5024,7 +5028,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="43057617"/>
+        <c:crossAx val="45945190"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5258,11 +5262,11 @@
         </c:ser>
         <c:gapWidth val="100"/>
         <c:overlap val="100"/>
-        <c:axId val="94251435"/>
-        <c:axId val="12623121"/>
+        <c:axId val="99987799"/>
+        <c:axId val="397805"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="94251435"/>
+        <c:axId val="99987799"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5295,7 +5299,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="12623121"/>
+        <c:crossAx val="397805"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -5303,7 +5307,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="12623121"/>
+        <c:axId val="397805"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5345,7 +5349,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="94251435"/>
+        <c:crossAx val="99987799"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5591,11 +5595,11 @@
         </c:ser>
         <c:gapWidth val="100"/>
         <c:overlap val="0"/>
-        <c:axId val="69585967"/>
-        <c:axId val="28000177"/>
+        <c:axId val="41894253"/>
+        <c:axId val="27770232"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="69585967"/>
+        <c:axId val="41894253"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5628,7 +5632,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="28000177"/>
+        <c:crossAx val="27770232"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -5636,7 +5640,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="28000177"/>
+        <c:axId val="27770232"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5678,7 +5682,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="69585967"/>
+        <c:crossAx val="41894253"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -6806,9 +6810,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>100800</xdr:colOff>
+      <xdr:colOff>100080</xdr:colOff>
       <xdr:row>87</xdr:row>
-      <xdr:rowOff>105840</xdr:rowOff>
+      <xdr:rowOff>105120</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -6817,7 +6821,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="2788920" y="11441160"/>
-        <a:ext cx="5752800" cy="3232800"/>
+        <a:ext cx="5752080" cy="3232080"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -6836,9 +6840,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>21</xdr:col>
-      <xdr:colOff>171000</xdr:colOff>
+      <xdr:colOff>170280</xdr:colOff>
       <xdr:row>87</xdr:row>
-      <xdr:rowOff>122040</xdr:rowOff>
+      <xdr:rowOff>121320</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -6847,7 +6851,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="11838960" y="11457360"/>
-        <a:ext cx="5752800" cy="3232800"/>
+        <a:ext cx="5752080" cy="3232080"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -6953,9 +6957,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>32</xdr:col>
-      <xdr:colOff>412920</xdr:colOff>
+      <xdr:colOff>412200</xdr:colOff>
       <xdr:row>205</xdr:row>
-      <xdr:rowOff>117360</xdr:rowOff>
+      <xdr:rowOff>116640</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -6964,7 +6968,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="21200760" y="29099520"/>
-        <a:ext cx="5752800" cy="3232800"/>
+        <a:ext cx="5752080" cy="3232080"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -6983,9 +6987,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>40</xdr:col>
-      <xdr:colOff>73800</xdr:colOff>
+      <xdr:colOff>73080</xdr:colOff>
       <xdr:row>201</xdr:row>
-      <xdr:rowOff>70560</xdr:rowOff>
+      <xdr:rowOff>69840</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -6994,7 +6998,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="27363960" y="28402200"/>
-        <a:ext cx="5752800" cy="3232800"/>
+        <a:ext cx="5752080" cy="3232080"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -7013,9 +7017,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>731880</xdr:colOff>
+      <xdr:colOff>731160</xdr:colOff>
       <xdr:row>209</xdr:row>
-      <xdr:rowOff>125280</xdr:rowOff>
+      <xdr:rowOff>124560</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -7024,7 +7028,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="9327600" y="29757600"/>
-        <a:ext cx="5752800" cy="3232800"/>
+        <a:ext cx="5752080" cy="3232080"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -7042,15 +7046,15 @@
   <xdr:twoCellAnchor editAs="absolute">
     <xdr:from>
       <xdr:col>11</xdr:col>
-      <xdr:colOff>22320</xdr:colOff>
+      <xdr:colOff>22680</xdr:colOff>
       <xdr:row>3</xdr:row>
       <xdr:rowOff>31680</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>788040</xdr:colOff>
+      <xdr:colOff>787680</xdr:colOff>
       <xdr:row>56</xdr:row>
-      <xdr:rowOff>93960</xdr:rowOff>
+      <xdr:rowOff>93240</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -7059,8 +7063,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm rot="4200">
-          <a:off x="9998280" y="519480"/>
-          <a:ext cx="4829760" cy="8677800"/>
+          <a:off x="9998640" y="519480"/>
+          <a:ext cx="4829040" cy="8677080"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7096,7 +7100,1459 @@
               <a:latin typeface="Arial"/>
               <a:ea typeface="DejaVu Sans"/>
             </a:rPr>
-            <a:t>Since 2020 META has tried to become something more than just an agent between the firms that want to make their product known to more than 3B daily users and the actual users that may want to buy the advertised product. It has failed with the “METAverse” idea but this experience brought them knowledge about what people are looking for. On top of that it’s broadly known that META is not an incredible innovator (Harvard already had it’s own internal chat before Facebook) but it is also true that Mark Zuckerberg is a great innovator, he perfectly knows how to improve an already existing product into something that everyone wants (MZ made Facebook worldwide dwarfing everything that has tried to compete with them). Instagram already existed, FB bought it and made it better, SNAP introduced stories to connect its users, INSTAGRAM took the idea and made it mainstream and now it is the most known feature in social media history. TIKTOK created the swipe mechanic to see videos, INSTAGRAM took it and made the REELS, …</a:t>
+            <a:t>Since </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>2020 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>META has </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>tried to </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>become </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>something </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>more than </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>just an </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>agent </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>between </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>the firms </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>that want </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>to make </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>their </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>product </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>known to </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>more than </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>3B daily </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>users and </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>the actual </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>users that </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>may want </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>to buy the </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>advertised </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>product. It </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>has failed </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>with the </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>“METAver</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>se” idea </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>but this </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>experienc</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>e brought </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>them </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>knowledge </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>about </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>what </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>people are </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>looking </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>for. On top </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>of that it’s </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>broadly </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>known </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>that META </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>is not an </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>incredible </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>innovator </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>(Harvard </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>already </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>had it’s </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>own </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>internal </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>chat </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>before </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>Facebook) </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>but it is </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>also true </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>that Mark </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>Zuckerber</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>g is a </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>great </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>innovator, </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>he </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>perfectly </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>knows </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>how to </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>improve </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>an already </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>existing </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>product </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>into </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>something </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>that </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>everyone </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>wants (MZ </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>made </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>Facebook </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>worldwide </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>dwarfing </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>everything </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>that has </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>tried to </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>compete </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>with </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>them). </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>Instagram </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>already </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>existed, </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>FB bought </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>it and </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>made it </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>better, </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>SNAP </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>introduced </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>stories to </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>connect its </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>users, </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>INSTAGR</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>AM took </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>the idea </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>and made </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>it </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>mainstrea</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>m and </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>now it is </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>the most </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>known </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>feature in </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>social </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>media </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>history. </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>TIKTOK </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>created </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>the swipe </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>mechanic </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>to see </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>videos, </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>INSTAGR</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>AM took it </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>and made </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>the </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>REELS, </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>…</a:t>
           </a:r>
           <a:endParaRPr lang="en-GB" sz="1200" b="0" u="none" strike="noStrike">
             <a:effectLst/>
@@ -7132,7 +8588,175 @@
               <a:latin typeface="Arial"/>
               <a:ea typeface="DejaVu Sans"/>
             </a:rPr>
-            <a:t>We are facing a pivotal time where something like that may repeat and for the first time with 2 products at the same time:</a:t>
+            <a:t>We are </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>facing a </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>pivotal </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>time </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>where </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>something </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>like that </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>may </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>repeat and </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>for the first </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>time with 2 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>products </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>at the </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>same </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>time:</a:t>
           </a:r>
           <a:endParaRPr lang="en-GB" sz="1200" b="0" u="none" strike="noStrike">
             <a:effectLst/>
@@ -7168,7 +8792,871 @@
               <a:latin typeface="Arial"/>
               <a:ea typeface="DejaVu Sans"/>
             </a:rPr>
-            <a:t>- META glasses, META’s partnership with the world leader in eyewear is a move that will force everyone to create their own glasses or to partner with other less known firms (like what GOOGL and SAMSUNG (005930.KS) are doing together GENTRE MONSTER and WARBY PARKER). And this idea doesn’t come out of the blue, it is an idea created by GOOGL in 2012 (failed project) and an idea that has been carried on by SNAP since 2016 with their camera glasses. META’s glasses were first shown in 2021 and since then they have been the sole customer choice for this kind of product (especially the AAPL’s vision pro fail).</a:t>
+            <a:t>- META </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>glasses, </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>META’s </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>partnershi</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>p with the </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>world </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>leader in </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>eyewear is </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>a move </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>that will </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>force </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>everyone </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>to create </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>their own </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>glasses or </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>to partner </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>with other </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>less </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>known </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>firms (like </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>what </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>GOOGL </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>and </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>SAMSUN</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>G </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>(005930.K</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>S) are </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>doing </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>together </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>GENTRE </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>MONSTE</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>R and </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>WARBY </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>PARKER). </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>And this </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>idea </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>doesn’t </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>come out </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>of the </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>blue, it is </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>an idea </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>created by </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>GOOGL in </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>2012 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>(failed </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>project) </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>and an </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>idea that </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>has been </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>carried on </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>by SNAP </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>since </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>2016 with </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>their </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>camera </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>glasses. </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>META’s </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>glasses </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>were first </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>shown in </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>2021 and </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>since then </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>they have </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>been the </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>sole </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>customer </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>choice for </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>this kind of </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>product </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>(especially </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>the AAPL’s </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>vision pro </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>fail).</a:t>
           </a:r>
           <a:endParaRPr lang="en-GB" sz="1200" b="0" u="none" strike="noStrike">
             <a:effectLst/>
@@ -7204,7 +9692,1147 @@
               <a:latin typeface="Arial"/>
               <a:ea typeface="DejaVu Sans"/>
             </a:rPr>
-            <a:t>- AI, META is investing and committing to invest billions of dollars in the new AI industry, this will lead to increase in efficiency, increase in services provided to the users and, which is the most important, will provide a better service to META’s customers that sign contracts with it every day to advertise their products. META’s AI set their main goal to create a personal super-intelligence for all of their users, this , like all other LLM, will create a new paradigm where firms will be willing to spend in order to be a preferred choice of the “personal-assistants”, like UBER for ride hailing or DASH to receive hot food at home or BKNG to book an hotel for the next holiday. This on top of the new additional information that the platform will be able to gather on their users in order to again increase UX and service provided to customers.</a:t>
+            <a:t>- AI, META </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>is </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>investing </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>and </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>committin</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>g to invest </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>billions of </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>dollars in </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>the new AI </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>industry, </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>this will </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>lead to </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>increase </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>in </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>efficiency, </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>increase </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>in services </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>provided </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>to the </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>users and, </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>which is </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>the most </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>important, </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>will </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>provide a </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>better </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>service to </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>META’s </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>customers </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>that sign </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>contracts </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>with it </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>every day </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>to </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>advertise </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>their </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>products. </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>META’s AI </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>set their </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>main goal </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>to create a </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>personal </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>super-</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>intelligenc</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>e for all of </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>their </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>users, this </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>, like all </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>other LLM, </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>will create </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>a new </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>paradigm </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>where </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>firms will </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>be willing </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>to spend </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>in order to </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>be a </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>preferred </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>choice of </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>the </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>“personal-</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>assistants”</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>, like </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>UBER for </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>ride </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>hailing or </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>DASH to </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>receive </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>hot food at </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>home or </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>BKNG to </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>book an </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>hotel for </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>the next </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>holiday. </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>This on </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>top of the </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>new </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>additional </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>informatio</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>n that the </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>platform </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>will be </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>able to </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>gather on </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>their users </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>in order to </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>again </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>increase </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>UX and </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>service </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>provided </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>to </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>customers</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>.</a:t>
           </a:r>
           <a:endParaRPr lang="en-GB" sz="1200" b="0" u="none" strike="noStrike">
             <a:effectLst/>
@@ -7240,7 +10868,631 @@
               <a:latin typeface="Arial"/>
               <a:ea typeface="DejaVu Sans"/>
             </a:rPr>
-            <a:t>On top of that, previous esperiements with TIKTOK have clearly shown that the “child-safety” practices are not working, like the limited-scrolling mechanic where every now and then the platform asks you if you are sure to keep using the app or stop doing something else. Therefore everything that the governments are trying to increase censorship (aka protect children) won’t affect META’s core business at the current status of the firm.</a:t>
+            <a:t>On top of </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>that, </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>previous </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>esperieme</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>nts with </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>TIKTOK </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>have </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>clearly </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>shown </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>that the </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>“child-</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>safety” </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>practices </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>are not </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>working, </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>like the </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>limited-</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>scrolling </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>mechanic </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>where </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>every now </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>and then </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>the </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>platform </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>asks you if </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>you are </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>sure to </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>keep </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>using the </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>app or </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>stop doing </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>something </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>else. </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>Therefore </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>everything </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>that the </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>governme</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>nts are </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>trying to </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>increase </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>censorshi</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>p (aka </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>protect </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>children) </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>won’t </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>affect </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>META’s </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>core </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>business </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>at the </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>current </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>status of </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:rPr>
+            <a:t>the firm.</a:t>
           </a:r>
           <a:endParaRPr lang="en-GB" sz="1200" b="0" u="none" strike="noStrike">
             <a:effectLst/>
@@ -7568,7 +11820,7 @@
       </c>
       <c r="E12" s="13" t="n">
         <f aca="false">+(F4/(F4+F6))*B17+(F6/(F4+F6))*B18*(1-0.11)</f>
-        <v>0.112193487547429</v>
+        <v>0.108897277026286</v>
       </c>
       <c r="F12" s="8"/>
       <c r="G12" s="4"/>
@@ -7685,8 +11937,8 @@
         <v>36</v>
       </c>
       <c r="B18" s="13" t="n">
-        <f aca="false">+0.0495 + (B19/10)</f>
-        <v>0.12754347826087</v>
+        <f aca="false">+0.0495 + (B19/100)</f>
+        <v>0.057304347826087</v>
       </c>
       <c r="C18" s="11"/>
       <c r="D18" s="14"/>
@@ -14367,36 +18619,36 @@
         <v>83344.61952</v>
       </c>
       <c r="AQ36" s="3" t="n">
-        <f aca="false">+AQ30*0.25</f>
-        <v>88746.5856</v>
+        <f aca="false">+AQ30*0.27</f>
+        <v>95846.312448</v>
       </c>
       <c r="AR36" s="3" t="n">
-        <f aca="false">+AR30*0.25</f>
-        <v>101171.107584</v>
+        <f aca="false">+AR30*0.27</f>
+        <v>109264.79619072</v>
       </c>
       <c r="AS36" s="3" t="n">
-        <f aca="false">+AS30*0.25</f>
-        <v>114323.35156992</v>
+        <f aca="false">+AS30*0.27</f>
+        <v>123469.219695514</v>
       </c>
       <c r="AT36" s="3" t="n">
-        <f aca="false">+AT30*0.2</f>
-        <v>102433.723006648</v>
+        <f aca="false">+AT30*0.25</f>
+        <v>128042.153758311</v>
       </c>
       <c r="AU36" s="3" t="n">
-        <f aca="false">+AU30*0.2</f>
-        <v>114725.769767446</v>
+        <f aca="false">+AU30*0.25</f>
+        <v>143407.212209308</v>
       </c>
       <c r="AV36" s="3" t="n">
-        <f aca="false">+AV30*0.2</f>
-        <v>128492.86213954</v>
+        <f aca="false">+AV30*0.25</f>
+        <v>160616.077674425</v>
       </c>
       <c r="AW36" s="3" t="n">
-        <f aca="false">+AW30*0.2</f>
-        <v>143912.005596284</v>
+        <f aca="false">+AW30*0.25</f>
+        <v>179890.006995356</v>
       </c>
       <c r="AX36" s="3" t="n">
-        <f aca="false">+AX30*0.2</f>
-        <v>161181.446267839</v>
+        <f aca="false">+AX30*0.25</f>
+        <v>201476.807834798</v>
       </c>
       <c r="AY36" s="3" t="n">
         <f aca="false">+AY30*0.2</f>
@@ -14554,35 +18806,35 @@
       </c>
       <c r="AQ37" s="35" t="n">
         <f aca="false">+AQ36/AQ$30</f>
-        <v>0.25</v>
+        <v>0.27</v>
       </c>
       <c r="AR37" s="35" t="n">
         <f aca="false">+AR36/AR$30</f>
-        <v>0.25</v>
+        <v>0.27</v>
       </c>
       <c r="AS37" s="35" t="n">
         <f aca="false">+AS36/AS$30</f>
-        <v>0.25</v>
+        <v>0.27</v>
       </c>
       <c r="AT37" s="35" t="n">
         <f aca="false">+AT36/AT$30</f>
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="AU37" s="35" t="n">
         <f aca="false">+AU36/AU$30</f>
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="AV37" s="35" t="n">
         <f aca="false">+AV36/AV$30</f>
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="AW37" s="35" t="n">
         <f aca="false">+AW36/AW$30</f>
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="AX37" s="35" t="n">
         <f aca="false">+AX36/AX$30</f>
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="AY37" s="35" t="n">
         <f aca="false">+AY36/AY$30</f>
@@ -14701,36 +18953,36 @@
         <v>21607.86432</v>
       </c>
       <c r="AQ38" s="3" t="n">
-        <f aca="false">+AQ30*0.05</f>
-        <v>17749.31712</v>
+        <f aca="false">+AQ30*0.07</f>
+        <v>24849.043968</v>
       </c>
       <c r="AR38" s="3" t="n">
-        <f aca="false">+AR30*0.05</f>
-        <v>20234.2215168</v>
+        <f aca="false">+AR30*0.07</f>
+        <v>28327.91012352</v>
       </c>
       <c r="AS38" s="3" t="n">
-        <f aca="false">+AS30*0.02</f>
-        <v>9145.8681255936</v>
+        <f aca="false">+AS30*0.07</f>
+        <v>32010.5384395776</v>
       </c>
       <c r="AT38" s="3" t="n">
-        <f aca="false">+AT30*0.02</f>
-        <v>10243.3723006648</v>
+        <f aca="false">+AT30*0.05</f>
+        <v>25608.4307516621</v>
       </c>
       <c r="AU38" s="3" t="n">
-        <f aca="false">+AU30*0.02</f>
-        <v>11472.5769767446</v>
+        <f aca="false">+AU30*0.05</f>
+        <v>28681.4424418616</v>
       </c>
       <c r="AV38" s="3" t="n">
-        <f aca="false">+AV30*0.02</f>
-        <v>12849.286213954</v>
+        <f aca="false">+AV30*0.05</f>
+        <v>32123.2155348849</v>
       </c>
       <c r="AW38" s="3" t="n">
-        <f aca="false">+AW30*0.02</f>
-        <v>14391.2005596284</v>
+        <f aca="false">+AW30*0.05</f>
+        <v>35978.0013990711</v>
       </c>
       <c r="AX38" s="3" t="n">
-        <f aca="false">+AX30*0.02</f>
-        <v>16118.1446267839</v>
+        <f aca="false">+AX30*0.05</f>
+        <v>40295.3615669597</v>
       </c>
       <c r="AY38" s="3" t="n">
         <f aca="false">+AY30*0.02</f>
@@ -14888,35 +19140,35 @@
       </c>
       <c r="AQ39" s="35" t="n">
         <f aca="false">+AQ38/AQ$30</f>
-        <v>0.05</v>
+        <v>0.07</v>
       </c>
       <c r="AR39" s="35" t="n">
         <f aca="false">+AR38/AR$30</f>
-        <v>0.05</v>
+        <v>0.07</v>
       </c>
       <c r="AS39" s="35" t="n">
         <f aca="false">+AS38/AS$30</f>
-        <v>0.02</v>
+        <v>0.07</v>
       </c>
       <c r="AT39" s="35" t="n">
         <f aca="false">+AT38/AT$30</f>
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
       <c r="AU39" s="35" t="n">
         <f aca="false">+AU38/AU$30</f>
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
       <c r="AV39" s="35" t="n">
         <f aca="false">+AV38/AV$30</f>
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
       <c r="AW39" s="35" t="n">
         <f aca="false">+AW38/AW$30</f>
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
       <c r="AX39" s="35" t="n">
         <f aca="false">+AX38/AX$30</f>
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
       <c r="AY39" s="35" t="n">
         <f aca="false">+AY38/AY$30</f>
@@ -15035,40 +19287,40 @@
         <v>18521.02656</v>
       </c>
       <c r="AQ40" s="3" t="n">
-        <f aca="false">+AQ30*0.05</f>
-        <v>17749.31712</v>
+        <f aca="false">+AQ30*0.06</f>
+        <v>21299.180544</v>
       </c>
       <c r="AR40" s="3" t="n">
-        <f aca="false">+AR30*0.05</f>
-        <v>20234.2215168</v>
+        <f aca="false">+AR30*0.06</f>
+        <v>24281.06582016</v>
       </c>
       <c r="AS40" s="3" t="n">
-        <f aca="false">+AS30*0.05</f>
-        <v>22864.670313984</v>
+        <f aca="false">+AS30*0.06</f>
+        <v>27437.6043767808</v>
       </c>
       <c r="AT40" s="3" t="n">
-        <f aca="false">+AT30*0.05</f>
-        <v>25608.4307516621</v>
+        <f aca="false">+AT30*0.06</f>
+        <v>30730.1169019945</v>
       </c>
       <c r="AU40" s="3" t="n">
         <f aca="false">+AU30*0.05</f>
         <v>28681.4424418616</v>
       </c>
       <c r="AV40" s="3" t="n">
-        <f aca="false">+AV30*0.03</f>
-        <v>19273.9293209309</v>
+        <f aca="false">+AV30*0.05</f>
+        <v>32123.2155348849</v>
       </c>
       <c r="AW40" s="3" t="n">
-        <f aca="false">+AW30*0.03</f>
-        <v>21586.8008394427</v>
+        <f aca="false">+AW30*0.05</f>
+        <v>35978.0013990711</v>
       </c>
       <c r="AX40" s="3" t="n">
-        <f aca="false">+AX30*0.03</f>
-        <v>24177.2169401758</v>
+        <f aca="false">+AX30*0.05</f>
+        <v>40295.3615669597</v>
       </c>
       <c r="AY40" s="3" t="n">
-        <f aca="false">+AY30*0.03</f>
-        <v>27078.4829729969</v>
+        <f aca="false">+AY30*0.05</f>
+        <v>45130.8049549948</v>
       </c>
     </row>
     <row r="41" s="35" customFormat="true" ht="10.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15222,19 +19474,19 @@
       </c>
       <c r="AQ41" s="35" t="n">
         <f aca="false">+AQ40/AQ$30</f>
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="AR41" s="35" t="n">
         <f aca="false">+AR40/AR$30</f>
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="AS41" s="35" t="n">
         <f aca="false">+AS40/AS$30</f>
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="AT41" s="35" t="n">
         <f aca="false">+AT40/AT$30</f>
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="AU41" s="35" t="n">
         <f aca="false">+AU40/AU$30</f>
@@ -15242,19 +19494,19 @@
       </c>
       <c r="AV41" s="35" t="n">
         <f aca="false">+AV40/AV$30</f>
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="AW41" s="35" t="n">
         <f aca="false">+AW40/AW$30</f>
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="AX41" s="35" t="n">
         <f aca="false">+AX40/AX$30</f>
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="AY41" s="35" t="n">
         <f aca="false">+AY40/AY$30</f>
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15411,39 +19663,39 @@
       </c>
       <c r="AQ42" s="3" t="n">
         <f aca="false">+AQ40+AQ38+AQ36</f>
-        <v>124245.21984</v>
+        <v>141994.53696</v>
       </c>
       <c r="AR42" s="3" t="n">
         <f aca="false">+AR40+AR38+AR36</f>
-        <v>141639.5506176</v>
+        <v>161873.7721344</v>
       </c>
       <c r="AS42" s="3" t="n">
         <f aca="false">+AS40+AS38+AS36</f>
-        <v>146333.890009498</v>
+        <v>182917.362511872</v>
       </c>
       <c r="AT42" s="3" t="n">
         <f aca="false">+AT40+AT38+AT36</f>
-        <v>138285.526058975</v>
+        <v>184380.701411967</v>
       </c>
       <c r="AU42" s="3" t="n">
         <f aca="false">+AU40+AU38+AU36</f>
-        <v>154879.789186052</v>
+        <v>200770.097093031</v>
       </c>
       <c r="AV42" s="3" t="n">
         <f aca="false">+AV40+AV38+AV36</f>
-        <v>160616.077674425</v>
+        <v>224862.508744194</v>
       </c>
       <c r="AW42" s="3" t="n">
         <f aca="false">+AW40+AW38+AW36</f>
-        <v>179890.006995356</v>
+        <v>251846.009793498</v>
       </c>
       <c r="AX42" s="3" t="n">
         <f aca="false">+AX40+AX38+AX36</f>
-        <v>201476.807834798</v>
+        <v>282067.530968718</v>
       </c>
       <c r="AY42" s="3" t="n">
         <f aca="false">+AY40+AY38+AY36</f>
-        <v>225654.024774974</v>
+        <v>243706.346756972</v>
       </c>
     </row>
     <row r="43" s="35" customFormat="true" ht="10.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15597,39 +19849,39 @@
       </c>
       <c r="AQ43" s="35" t="n">
         <f aca="false">+AQ42/AQ$30</f>
-        <v>0.35</v>
+        <v>0.4</v>
       </c>
       <c r="AR43" s="35" t="n">
         <f aca="false">+AR42/AR$30</f>
-        <v>0.35</v>
+        <v>0.4</v>
       </c>
       <c r="AS43" s="35" t="n">
         <f aca="false">+AS42/AS$30</f>
-        <v>0.32</v>
+        <v>0.4</v>
       </c>
       <c r="AT43" s="35" t="n">
         <f aca="false">+AT42/AT$30</f>
-        <v>0.27</v>
+        <v>0.36</v>
       </c>
       <c r="AU43" s="35" t="n">
         <f aca="false">+AU42/AU$30</f>
-        <v>0.27</v>
+        <v>0.35</v>
       </c>
       <c r="AV43" s="35" t="n">
         <f aca="false">+AV42/AV$30</f>
-        <v>0.25</v>
+        <v>0.35</v>
       </c>
       <c r="AW43" s="35" t="n">
         <f aca="false">+AW42/AW$30</f>
-        <v>0.25</v>
+        <v>0.35</v>
       </c>
       <c r="AX43" s="35" t="n">
         <f aca="false">+AX42/AX$30</f>
-        <v>0.25</v>
+        <v>0.35</v>
       </c>
       <c r="AY43" s="35" t="n">
         <f aca="false">+AY42/AY$30</f>
-        <v>0.25</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15786,39 +20038,39 @@
       </c>
       <c r="AQ44" s="3" t="n">
         <f aca="false">AQ34-AQ42</f>
-        <v>170393.444352</v>
+        <v>152644.127232</v>
       </c>
       <c r="AR44" s="3" t="n">
         <f aca="false">AR34-AR42</f>
-        <v>194248.52656128</v>
+        <v>174014.30504448</v>
       </c>
       <c r="AS44" s="3" t="n">
         <f aca="false">AS34-AS42</f>
-        <v>237792.571265433</v>
+        <v>201209.098763059</v>
       </c>
       <c r="AT44" s="3" t="n">
         <f aca="false">AT34-AT42</f>
-        <v>291936.110568948</v>
+        <v>245840.935215956</v>
       </c>
       <c r="AU44" s="3" t="n">
         <f aca="false">AU34-AU42</f>
-        <v>326968.443837222</v>
+        <v>281078.135930243</v>
       </c>
       <c r="AV44" s="3" t="n">
         <f aca="false">AV34-AV42</f>
-        <v>385478.58641862</v>
+        <v>321232.15534885</v>
       </c>
       <c r="AW44" s="3" t="n">
         <f aca="false">AW34-AW42</f>
-        <v>431736.016788854</v>
+        <v>359780.013990711</v>
       </c>
       <c r="AX44" s="3" t="n">
         <f aca="false">AX34-AX42</f>
-        <v>483544.338803516</v>
+        <v>402953.615669597</v>
       </c>
       <c r="AY44" s="3" t="n">
         <f aca="false">AY34-AY42</f>
-        <v>541569.659459938</v>
+        <v>523517.33747794</v>
       </c>
     </row>
     <row r="45" s="35" customFormat="true" ht="10.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15972,39 +20224,39 @@
       </c>
       <c r="AQ45" s="35" t="n">
         <f aca="false">+AQ44/AQ$30</f>
-        <v>0.48</v>
+        <v>0.43</v>
       </c>
       <c r="AR45" s="35" t="n">
         <f aca="false">+AR44/AR$30</f>
-        <v>0.48</v>
+        <v>0.43</v>
       </c>
       <c r="AS45" s="35" t="n">
         <f aca="false">+AS44/AS$30</f>
-        <v>0.52</v>
+        <v>0.439999999999999</v>
       </c>
       <c r="AT45" s="35" t="n">
         <f aca="false">+AT44/AT$30</f>
-        <v>0.569999999999999</v>
+        <v>0.48</v>
       </c>
       <c r="AU45" s="35" t="n">
         <f aca="false">+AU44/AU$30</f>
-        <v>0.57</v>
+        <v>0.49</v>
       </c>
       <c r="AV45" s="35" t="n">
         <f aca="false">+AV44/AV$30</f>
-        <v>0.600000000000001</v>
+        <v>0.500000000000001</v>
       </c>
       <c r="AW45" s="35" t="n">
         <f aca="false">+AW44/AW$30</f>
-        <v>0.600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AX45" s="35" t="n">
         <f aca="false">+AX44/AX$30</f>
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AY45" s="35" t="n">
         <f aca="false">+AY44/AY$30</f>
-        <v>0.600000000000001</v>
+        <v>0.580000000000001</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16127,35 +20379,35 @@
       </c>
       <c r="AR46" s="3" t="n">
         <f aca="false">+AQ91*$BB$68</f>
-        <v>7518.46813299118</v>
+        <v>7216.72974195118</v>
       </c>
       <c r="AS46" s="3" t="n">
         <f aca="false">+AR91*$BB$68</f>
-        <v>10343.206058711</v>
+        <v>9753.96422896122</v>
       </c>
       <c r="AT46" s="3" t="n">
         <f aca="false">+AS91*$BB$68</f>
-        <v>13817.106941249</v>
+        <v>12707.4471108495</v>
       </c>
       <c r="AU46" s="3" t="n">
         <f aca="false">+AT91*$BB$68</f>
-        <v>18097.6519863918</v>
+        <v>16327.1244634248</v>
       </c>
       <c r="AV46" s="3" t="n">
         <f aca="false">+AU91*$BB$68</f>
-        <v>22928.5773279223</v>
+        <v>20490.7981089361</v>
       </c>
       <c r="AW46" s="3" t="n">
         <f aca="false">+AV91*$BB$68</f>
-        <v>28646.2776203739</v>
+        <v>25274.9194573451</v>
       </c>
       <c r="AX46" s="3" t="n">
         <f aca="false">+AW91*$BB$68</f>
-        <v>35091.6297421031</v>
+        <v>30665.6885256179</v>
       </c>
       <c r="AY46" s="3" t="n">
         <f aca="false">+AX91*$BB$68</f>
-        <v>42352.5333017418</v>
+        <v>36736.3587843509</v>
       </c>
     </row>
     <row r="47" s="35" customFormat="true" ht="10.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16313,35 +20565,35 @@
       </c>
       <c r="AR47" s="35" t="n">
         <f aca="false">+AR46/AR$30</f>
-        <v>0.018578594997462</v>
+        <v>0.0178329809623743</v>
       </c>
       <c r="AS47" s="35" t="n">
         <f aca="false">+AS46/AS$30</f>
-        <v>0.02261831444905</v>
+        <v>0.0213297722972102</v>
       </c>
       <c r="AT47" s="35" t="n">
         <f aca="false">+AT46/AT$30</f>
-        <v>0.0269776525458363</v>
+        <v>0.0248110617047957</v>
       </c>
       <c r="AU47" s="35" t="n">
         <f aca="false">+AU46/AU$30</f>
-        <v>0.0315494104298911</v>
+        <v>0.0284628719363061</v>
       </c>
       <c r="AV47" s="35" t="n">
         <f aca="false">+AV46/AV$30</f>
-        <v>0.0356884840856336</v>
+        <v>0.0318940644137628</v>
       </c>
       <c r="AW47" s="35" t="n">
         <f aca="false">+AW46/AW$30</f>
-        <v>0.0398108239846718</v>
+        <v>0.035125519031746</v>
       </c>
       <c r="AX47" s="35" t="n">
         <f aca="false">+AX46/AX$30</f>
-        <v>0.0435430138575511</v>
+        <v>0.0380511395519558</v>
       </c>
       <c r="AY47" s="35" t="n">
         <f aca="false">+AY46/AY$30</f>
-        <v>0.0469219786174614</v>
+        <v>0.0406998709872171</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16498,39 +20750,39 @@
       </c>
       <c r="AQ48" s="3" t="n">
         <f aca="false">AQ44+AQ46</f>
-        <v>174937.967045222</v>
+        <v>157188.649925222</v>
       </c>
       <c r="AR48" s="3" t="n">
         <f aca="false">AR44+AR46</f>
-        <v>201766.994694271</v>
+        <v>181231.034786431</v>
       </c>
       <c r="AS48" s="3" t="n">
         <f aca="false">AS44+AS46</f>
-        <v>248135.777324144</v>
+        <v>210963.06299202</v>
       </c>
       <c r="AT48" s="3" t="n">
         <f aca="false">AT44+AT46</f>
-        <v>305753.217510197</v>
+        <v>258548.382326805</v>
       </c>
       <c r="AU48" s="3" t="n">
         <f aca="false">AU44+AU46</f>
-        <v>345066.095823613</v>
+        <v>297405.260393668</v>
       </c>
       <c r="AV48" s="3" t="n">
         <f aca="false">AV44+AV46</f>
-        <v>408407.163746542</v>
+        <v>341722.953457786</v>
       </c>
       <c r="AW48" s="3" t="n">
         <f aca="false">AW44+AW46</f>
-        <v>460382.294409228</v>
+        <v>385054.933448056</v>
       </c>
       <c r="AX48" s="3" t="n">
         <f aca="false">AX44+AX46</f>
-        <v>518635.968545619</v>
+        <v>433619.304195214</v>
       </c>
       <c r="AY48" s="3" t="n">
         <f aca="false">AY44+AY46</f>
-        <v>583922.19276168</v>
+        <v>560253.696262291</v>
       </c>
     </row>
     <row r="49" s="35" customFormat="true" ht="10.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16684,39 +20936,39 @@
       </c>
       <c r="AQ49" s="35" t="n">
         <f aca="false">+AQ48/AQ$30</f>
-        <v>0.49280196489391</v>
+        <v>0.44280196489391</v>
       </c>
       <c r="AR49" s="35" t="n">
         <f aca="false">+AR48/AR$30</f>
-        <v>0.498578594997462</v>
+        <v>0.447832980962374</v>
       </c>
       <c r="AS49" s="35" t="n">
         <f aca="false">+AS48/AS$30</f>
-        <v>0.54261831444905</v>
+        <v>0.46132977229721</v>
       </c>
       <c r="AT49" s="35" t="n">
         <f aca="false">+AT48/AT$30</f>
-        <v>0.596977652545836</v>
+        <v>0.504811061704795</v>
       </c>
       <c r="AU49" s="35" t="n">
         <f aca="false">+AU48/AU$30</f>
-        <v>0.601549410429891</v>
+        <v>0.518462871936306</v>
       </c>
       <c r="AV49" s="35" t="n">
         <f aca="false">+AV48/AV$30</f>
-        <v>0.635688484085635</v>
+        <v>0.531894064413764</v>
       </c>
       <c r="AW49" s="35" t="n">
         <f aca="false">+AW48/AW$30</f>
-        <v>0.639810823984672</v>
+        <v>0.535125519031746</v>
       </c>
       <c r="AX49" s="35" t="n">
         <f aca="false">+AX48/AX$30</f>
-        <v>0.643543013857551</v>
+        <v>0.538051139551956</v>
       </c>
       <c r="AY49" s="35" t="n">
         <f aca="false">+AY48/AY$30</f>
-        <v>0.646921978617462</v>
+        <v>0.620699870987218</v>
       </c>
     </row>
     <row r="50" s="51" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16845,39 +21097,39 @@
       </c>
       <c r="AQ50" s="3" t="n">
         <f aca="false">+AQ48*0.15</f>
-        <v>26240.6950567834</v>
+        <v>23578.2974887834</v>
       </c>
       <c r="AR50" s="3" t="n">
         <f aca="false">+AR48*0.3</f>
-        <v>60530.0984082813</v>
+        <v>54369.3104359294</v>
       </c>
       <c r="AS50" s="3" t="n">
         <f aca="false">+AS48*0.3</f>
-        <v>74440.7331972433</v>
+        <v>63288.9188976061</v>
       </c>
       <c r="AT50" s="3" t="n">
         <f aca="false">+AT48*0.3</f>
-        <v>91725.965253059</v>
+        <v>77564.5146980416</v>
       </c>
       <c r="AU50" s="3" t="n">
         <f aca="false">+AU48*0.3</f>
-        <v>103519.828747084</v>
+        <v>89221.5781181004</v>
       </c>
       <c r="AV50" s="3" t="n">
         <f aca="false">+AV48*0.3</f>
-        <v>122522.149123963</v>
+        <v>102516.886037336</v>
       </c>
       <c r="AW50" s="3" t="n">
         <f aca="false">+AW48*0.3</f>
-        <v>138114.688322768</v>
+        <v>115516.480034417</v>
       </c>
       <c r="AX50" s="3" t="n">
         <f aca="false">+AX48*0.3</f>
-        <v>155590.790563686</v>
+        <v>130085.791258564</v>
       </c>
       <c r="AY50" s="3" t="n">
         <f aca="false">+AY48*0.3</f>
-        <v>175176.657828504</v>
+        <v>168076.108878687</v>
       </c>
       <c r="AZ50" s="3"/>
       <c r="BA50" s="3"/>
@@ -17133,39 +21385,39 @@
       </c>
       <c r="AQ51" s="35" t="n">
         <f aca="false">+AQ50/AQ$30</f>
-        <v>0.0739202947340865</v>
+        <v>0.0664202947340865</v>
       </c>
       <c r="AR51" s="35" t="n">
         <f aca="false">+AR50/AR$30</f>
-        <v>0.149573578499239</v>
+        <v>0.134349894288712</v>
       </c>
       <c r="AS51" s="35" t="n">
         <f aca="false">+AS50/AS$30</f>
-        <v>0.162785494334715</v>
+        <v>0.138398931689163</v>
       </c>
       <c r="AT51" s="35" t="n">
         <f aca="false">+AT50/AT$30</f>
-        <v>0.179093295763751</v>
+        <v>0.151443318511439</v>
       </c>
       <c r="AU51" s="35" t="n">
         <f aca="false">+AU50/AU$30</f>
-        <v>0.180464823128967</v>
+        <v>0.155538861580892</v>
       </c>
       <c r="AV51" s="35" t="n">
         <f aca="false">+AV50/AV$30</f>
-        <v>0.19070654522569</v>
+        <v>0.159568219324129</v>
       </c>
       <c r="AW51" s="35" t="n">
         <f aca="false">+AW50/AW$30</f>
-        <v>0.191943247195402</v>
+        <v>0.160537655709524</v>
       </c>
       <c r="AX51" s="35" t="n">
         <f aca="false">+AX50/AX$30</f>
-        <v>0.193062904157265</v>
+        <v>0.161415341865587</v>
       </c>
       <c r="AY51" s="35" t="n">
         <f aca="false">+AY50/AY$30</f>
-        <v>0.194076593585239</v>
+        <v>0.186209961296165</v>
       </c>
       <c r="AZ51" s="35"/>
       <c r="BA51" s="35"/>
@@ -17423,419 +21675,419 @@
       </c>
       <c r="AQ52" s="51" t="n">
         <f aca="false">AQ48-AQ50</f>
-        <v>148697.271988439</v>
+        <v>133610.352436439</v>
       </c>
       <c r="AR52" s="51" t="n">
         <f aca="false">AR48-AR50</f>
-        <v>141236.89628599</v>
+        <v>126861.724350502</v>
       </c>
       <c r="AS52" s="51" t="n">
         <f aca="false">AS48-AS50</f>
-        <v>173695.044126901</v>
+        <v>147674.144094414</v>
       </c>
       <c r="AT52" s="51" t="n">
         <f aca="false">AT48-AT50</f>
-        <v>214027.252257138</v>
+        <v>180983.867628764</v>
       </c>
       <c r="AU52" s="51" t="n">
         <f aca="false">AU48-AU50</f>
-        <v>241546.267076529</v>
+        <v>208183.682275568</v>
       </c>
       <c r="AV52" s="51" t="n">
         <f aca="false">AV48-AV50</f>
-        <v>285885.014622579</v>
+        <v>239206.06742045</v>
       </c>
       <c r="AW52" s="51" t="n">
         <f aca="false">AW48-AW50</f>
-        <v>322267.606086459</v>
+        <v>269538.45341364</v>
       </c>
       <c r="AX52" s="51" t="n">
         <f aca="false">AX48-AX50</f>
-        <v>363045.177981933</v>
+        <v>303533.51293665</v>
       </c>
       <c r="AY52" s="51" t="n">
         <f aca="false">AY48-AY50</f>
-        <v>408745.534933176</v>
+        <v>392177.587383604</v>
       </c>
       <c r="AZ52" s="51" t="n">
         <f aca="false">+AY52*(1+$BB$66)</f>
-        <v>412832.990282508</v>
+        <v>400021.139131276</v>
       </c>
       <c r="BA52" s="51" t="n">
         <f aca="false">+AZ52*(1+$BB$66)</f>
-        <v>416961.320185333</v>
+        <v>408021.561913902</v>
       </c>
       <c r="BB52" s="51" t="n">
         <f aca="false">+BA52*(1+$BB$66)</f>
-        <v>421130.933387186</v>
+        <v>416181.99315218</v>
       </c>
       <c r="BC52" s="51" t="n">
         <f aca="false">+BB52*(1+$BB$66)</f>
-        <v>425342.242721058</v>
+        <v>424505.633015223</v>
       </c>
       <c r="BD52" s="51" t="n">
         <f aca="false">+BC52*(1+$BB$66)</f>
-        <v>429595.665148269</v>
+        <v>432995.745675528</v>
       </c>
       <c r="BE52" s="51" t="n">
         <f aca="false">+BD52*(1+$BB$66)</f>
-        <v>433891.621799751</v>
+        <v>441655.660589038</v>
       </c>
       <c r="BF52" s="51" t="n">
         <f aca="false">+BE52*(1+$BB$66)</f>
-        <v>438230.538017749</v>
+        <v>450488.773800819</v>
       </c>
       <c r="BG52" s="51" t="n">
         <f aca="false">+BF52*(1+$BB$66)</f>
-        <v>442612.843397926</v>
+        <v>459498.549276836</v>
       </c>
       <c r="BH52" s="51" t="n">
         <f aca="false">+BG52*(1+$BB$66)</f>
-        <v>447038.971831906</v>
+        <v>468688.520262372</v>
       </c>
       <c r="BI52" s="51" t="n">
         <f aca="false">+BH52*(1+$BB$66)</f>
-        <v>451509.361550225</v>
+        <v>478062.29066762</v>
       </c>
       <c r="BJ52" s="51" t="n">
         <f aca="false">+BI52*(1+$BB$66)</f>
-        <v>456024.455165727</v>
+        <v>487623.536480972</v>
       </c>
       <c r="BK52" s="51" t="n">
         <f aca="false">+BJ52*(1+$BB$66)</f>
-        <v>460584.699717384</v>
+        <v>497376.007210592</v>
       </c>
       <c r="BL52" s="51" t="n">
         <f aca="false">+BK52*(1+$BB$66)</f>
-        <v>465190.546714558</v>
+        <v>507323.527354803</v>
       </c>
       <c r="BM52" s="51" t="n">
         <f aca="false">+BL52*(1+$BB$66)</f>
-        <v>469842.452181704</v>
+        <v>517469.997901899</v>
       </c>
       <c r="BN52" s="51" t="n">
         <f aca="false">+BM52*(1+$BB$66)</f>
-        <v>474540.876703521</v>
+        <v>527819.397859937</v>
       </c>
       <c r="BO52" s="51" t="n">
         <f aca="false">+BN52*(1+$BB$66)</f>
-        <v>479286.285470556</v>
+        <v>538375.785817136</v>
       </c>
       <c r="BP52" s="51" t="n">
         <f aca="false">+BO52*(1+$BB$66)</f>
-        <v>484079.148325261</v>
+        <v>549143.301533479</v>
       </c>
       <c r="BQ52" s="51" t="n">
         <f aca="false">+BP52*(1+$BB$66)</f>
-        <v>488919.939808514</v>
+        <v>560126.167564148</v>
       </c>
       <c r="BR52" s="51" t="n">
         <f aca="false">+BQ52*(1+$BB$66)</f>
-        <v>493809.139206599</v>
+        <v>571328.690915431</v>
       </c>
       <c r="BS52" s="51" t="n">
         <f aca="false">+BR52*(1+$BB$66)</f>
-        <v>498747.230598665</v>
+        <v>582755.26473374</v>
       </c>
       <c r="BT52" s="51" t="n">
         <f aca="false">+BS52*(1+$BB$66)</f>
-        <v>503734.702904652</v>
+        <v>594410.370028415</v>
       </c>
       <c r="BU52" s="51" t="n">
         <f aca="false">+BT52*(1+$BB$66)</f>
-        <v>508772.049933698</v>
+        <v>606298.577428983</v>
       </c>
       <c r="BV52" s="51" t="n">
         <f aca="false">+BU52*(1+$BB$66)</f>
-        <v>513859.770433035</v>
+        <v>618424.548977563</v>
       </c>
       <c r="BW52" s="51" t="n">
         <f aca="false">+BV52*(1+$BB$66)</f>
-        <v>518998.368137366</v>
+        <v>630793.039957114</v>
       </c>
       <c r="BX52" s="51" t="n">
         <f aca="false">+BW52*(1+$BB$66)</f>
-        <v>524188.351818739</v>
+        <v>643408.900756256</v>
       </c>
       <c r="BY52" s="51" t="n">
         <f aca="false">+BX52*(1+$BB$66)</f>
-        <v>529430.235336927</v>
+        <v>656277.078771381</v>
       </c>
       <c r="BZ52" s="51" t="n">
         <f aca="false">+BY52*(1+$BB$66)</f>
-        <v>534724.537690296</v>
+        <v>669402.620346809</v>
       </c>
       <c r="CA52" s="51" t="n">
         <f aca="false">+BZ52*(1+$BB$66)</f>
-        <v>540071.783067199</v>
+        <v>682790.672753745</v>
       </c>
       <c r="CB52" s="51" t="n">
         <f aca="false">+CA52*(1+$BB$66)</f>
-        <v>545472.500897871</v>
+        <v>696446.48620882</v>
       </c>
       <c r="CC52" s="51" t="n">
         <f aca="false">+CB52*(1+$BB$66)</f>
-        <v>550927.22590685</v>
+        <v>710375.415932997</v>
       </c>
       <c r="CD52" s="51" t="n">
         <f aca="false">+CC52*(1+$BB$66)</f>
-        <v>556436.498165918</v>
+        <v>724582.924251657</v>
       </c>
       <c r="CE52" s="51" t="n">
         <f aca="false">+CD52*(1+$BB$66)</f>
-        <v>562000.863147578</v>
+        <v>739074.58273669</v>
       </c>
       <c r="CF52" s="51" t="n">
         <f aca="false">+CE52*(1+$BB$66)</f>
-        <v>567620.871779053</v>
+        <v>753856.074391424</v>
       </c>
       <c r="CG52" s="51" t="n">
         <f aca="false">+CF52*(1+$BB$66)</f>
-        <v>573297.080496844</v>
+        <v>768933.195879252</v>
       </c>
       <c r="CH52" s="51" t="n">
         <f aca="false">+CG52*(1+$BB$66)</f>
-        <v>579030.051301812</v>
+        <v>784311.859796837</v>
       </c>
       <c r="CI52" s="51" t="n">
         <f aca="false">+CH52*(1+$BB$66)</f>
-        <v>584820.351814831</v>
+        <v>799998.096992774</v>
       </c>
       <c r="CJ52" s="51" t="n">
         <f aca="false">+CI52*(1+$BB$66)</f>
-        <v>590668.555332979</v>
+        <v>815998.058932629</v>
       </c>
       <c r="CK52" s="51" t="n">
         <f aca="false">+CJ52*(1+$BB$66)</f>
-        <v>596575.240886309</v>
+        <v>832318.020111282</v>
       </c>
       <c r="CL52" s="51" t="n">
         <f aca="false">+CK52*(1+$BB$66)</f>
-        <v>602540.993295172</v>
+        <v>848964.380513507</v>
       </c>
       <c r="CM52" s="51" t="n">
         <f aca="false">+CL52*(1+$BB$66)</f>
-        <v>608566.403228123</v>
+        <v>865943.668123778</v>
       </c>
       <c r="CN52" s="51" t="n">
         <f aca="false">+CM52*(1+$BB$66)</f>
-        <v>614652.067260405</v>
+        <v>883262.541486253</v>
       </c>
       <c r="CO52" s="51" t="n">
         <f aca="false">+CN52*(1+$BB$66)</f>
-        <v>620798.587933009</v>
+        <v>900927.792315978</v>
       </c>
       <c r="CP52" s="51" t="n">
         <f aca="false">+CO52*(1+$BB$66)</f>
-        <v>627006.573812339</v>
+        <v>918946.348162298</v>
       </c>
       <c r="CQ52" s="51" t="n">
         <f aca="false">+CP52*(1+$BB$66)</f>
-        <v>633276.639550462</v>
+        <v>937325.275125544</v>
       </c>
       <c r="CR52" s="51" t="n">
         <f aca="false">+CQ52*(1+$BB$66)</f>
-        <v>639609.405945967</v>
+        <v>956071.780628055</v>
       </c>
       <c r="CS52" s="51" t="n">
         <f aca="false">+CR52*(1+$BB$66)</f>
-        <v>646005.500005426</v>
+        <v>975193.216240616</v>
       </c>
       <c r="CT52" s="51" t="n">
         <f aca="false">+CS52*(1+$BB$66)</f>
-        <v>652465.555005481</v>
+        <v>994697.080565428</v>
       </c>
       <c r="CU52" s="51" t="n">
         <f aca="false">+CT52*(1+$BB$66)</f>
-        <v>658990.210555536</v>
+        <v>1014591.02217674</v>
       </c>
       <c r="CV52" s="51" t="n">
         <f aca="false">+CU52*(1+$BB$66)</f>
-        <v>665580.112661091</v>
+        <v>1034882.84262027</v>
       </c>
       <c r="CW52" s="51" t="n">
         <f aca="false">+CV52*(1+$BB$66)</f>
-        <v>672235.913787702</v>
+        <v>1055580.49947268</v>
       </c>
       <c r="CX52" s="51" t="n">
         <f aca="false">+CW52*(1+$BB$66)</f>
-        <v>678958.272925579</v>
+        <v>1076692.10946213</v>
       </c>
       <c r="CY52" s="51" t="n">
         <f aca="false">+CX52*(1+$BB$66)</f>
-        <v>685747.855654835</v>
+        <v>1098225.95165137</v>
       </c>
       <c r="CZ52" s="51" t="n">
         <f aca="false">+CY52*(1+$BB$66)</f>
-        <v>692605.334211383</v>
+        <v>1120190.4706844</v>
       </c>
       <c r="DA52" s="51" t="n">
         <f aca="false">+CZ52*(1+$BB$66)</f>
-        <v>699531.387553497</v>
+        <v>1142594.28009809</v>
       </c>
       <c r="DB52" s="51" t="n">
         <f aca="false">+DA52*(1+$BB$66)</f>
-        <v>706526.701429032</v>
+        <v>1165446.16570005</v>
       </c>
       <c r="DC52" s="51" t="n">
         <f aca="false">+DB52*(1+$BB$66)</f>
-        <v>713591.968443322</v>
+        <v>1188755.08901405</v>
       </c>
       <c r="DD52" s="51" t="n">
         <f aca="false">+DC52*(1+$BB$66)</f>
-        <v>720727.888127755</v>
+        <v>1212530.19079433</v>
       </c>
       <c r="DE52" s="51" t="n">
         <f aca="false">+DD52*(1+$BB$66)</f>
-        <v>727935.167009033</v>
+        <v>1236780.79461022</v>
       </c>
       <c r="DF52" s="51" t="n">
         <f aca="false">+DE52*(1+$BB$66)</f>
-        <v>735214.518679123</v>
+        <v>1261516.41050242</v>
       </c>
       <c r="DG52" s="51" t="n">
         <f aca="false">+DF52*(1+$BB$66)</f>
-        <v>742566.663865915</v>
+        <v>1286746.73871247</v>
       </c>
       <c r="DH52" s="51" t="n">
         <f aca="false">+DG52*(1+$BB$66)</f>
-        <v>749992.330504574</v>
+        <v>1312481.67348672</v>
       </c>
       <c r="DI52" s="51" t="n">
         <f aca="false">+DH52*(1+$BB$66)</f>
-        <v>757492.253809619</v>
+        <v>1338731.30695646</v>
       </c>
       <c r="DJ52" s="51" t="n">
         <f aca="false">+DI52*(1+$BB$66)</f>
-        <v>765067.176347716</v>
+        <v>1365505.93309558</v>
       </c>
       <c r="DK52" s="51" t="n">
         <f aca="false">+DJ52*(1+$BB$66)</f>
-        <v>772717.848111193</v>
+        <v>1392816.0517575</v>
       </c>
       <c r="DL52" s="51" t="n">
         <f aca="false">+DK52*(1+$BB$66)</f>
-        <v>780445.026592305</v>
+        <v>1420672.37279265</v>
       </c>
       <c r="DM52" s="51" t="n">
         <f aca="false">+DL52*(1+$BB$66)</f>
-        <v>788249.476858228</v>
+        <v>1449085.8202485</v>
       </c>
       <c r="DN52" s="51" t="n">
         <f aca="false">+DM52*(1+$BB$66)</f>
-        <v>796131.97162681</v>
+        <v>1478067.53665347</v>
       </c>
       <c r="DO52" s="51" t="n">
         <f aca="false">+DN52*(1+$BB$66)</f>
-        <v>804093.291343078</v>
+        <v>1507628.88738654</v>
       </c>
       <c r="DP52" s="51" t="n">
         <f aca="false">+DO52*(1+$BB$66)</f>
-        <v>812134.224256509</v>
+        <v>1537781.46513427</v>
       </c>
       <c r="DQ52" s="51" t="n">
         <f aca="false">+DP52*(1+$BB$66)</f>
-        <v>820255.566499074</v>
+        <v>1568537.09443696</v>
       </c>
       <c r="DR52" s="51" t="n">
         <f aca="false">+DQ52*(1+$BB$66)</f>
-        <v>828458.122164065</v>
+        <v>1599907.83632569</v>
       </c>
       <c r="DS52" s="51" t="n">
         <f aca="false">+DR52*(1+$BB$66)</f>
-        <v>836742.703385705</v>
+        <v>1631905.99305221</v>
       </c>
       <c r="DT52" s="51" t="n">
         <f aca="false">+DS52*(1+$BB$66)</f>
-        <v>845110.130419563</v>
+        <v>1664544.11291325</v>
       </c>
       <c r="DU52" s="51" t="n">
         <f aca="false">+DT52*(1+$BB$66)</f>
-        <v>853561.231723758</v>
+        <v>1697834.99517152</v>
       </c>
       <c r="DV52" s="51" t="n">
         <f aca="false">+DU52*(1+$BB$66)</f>
-        <v>862096.844040996</v>
+        <v>1731791.69507495</v>
       </c>
       <c r="DW52" s="51" t="n">
         <f aca="false">+DV52*(1+$BB$66)</f>
-        <v>870717.812481406</v>
+        <v>1766427.52897645</v>
       </c>
       <c r="DX52" s="51" t="n">
         <f aca="false">+DW52*(1+$BB$66)</f>
-        <v>879424.99060622</v>
+        <v>1801756.07955598</v>
       </c>
       <c r="DY52" s="51" t="n">
         <f aca="false">+DX52*(1+$BB$66)</f>
-        <v>888219.240512282</v>
+        <v>1837791.2011471</v>
       </c>
       <c r="DZ52" s="51" t="n">
         <f aca="false">+DY52*(1+$BB$66)</f>
-        <v>897101.432917405</v>
+        <v>1874547.02517004</v>
       </c>
       <c r="EA52" s="51" t="n">
         <f aca="false">+DZ52*(1+$BB$66)</f>
-        <v>906072.447246579</v>
+        <v>1912037.96567344</v>
       </c>
       <c r="EB52" s="51" t="n">
         <f aca="false">+EA52*(1+$BB$66)</f>
-        <v>915133.171719044</v>
+        <v>1950278.72498691</v>
       </c>
       <c r="EC52" s="51" t="n">
         <f aca="false">+EB52*(1+$BB$66)</f>
-        <v>924284.503436235</v>
+        <v>1989284.29948665</v>
       </c>
       <c r="ED52" s="51" t="n">
         <f aca="false">+EC52*(1+$BB$66)</f>
-        <v>933527.348470597</v>
+        <v>2029069.98547638</v>
       </c>
       <c r="EE52" s="51" t="n">
         <f aca="false">+ED52*(1+$BB$66)</f>
-        <v>942862.621955303</v>
+        <v>2069651.38518591</v>
       </c>
       <c r="EF52" s="51" t="n">
         <f aca="false">+EE52*(1+$BB$66)</f>
-        <v>952291.248174856</v>
+        <v>2111044.41288962</v>
       </c>
       <c r="EG52" s="51" t="n">
         <f aca="false">+EF52*(1+$BB$66)</f>
-        <v>961814.160656605</v>
+        <v>2153265.30114742</v>
       </c>
       <c r="EH52" s="51" t="n">
         <f aca="false">+EG52*(1+$BB$66)</f>
-        <v>971432.302263171</v>
+        <v>2196330.60717037</v>
       </c>
       <c r="EI52" s="51" t="n">
         <f aca="false">+EH52*(1+$BB$66)</f>
-        <v>981146.625285803</v>
+        <v>2240257.21931377</v>
       </c>
       <c r="EJ52" s="51" t="n">
         <f aca="false">+EI52*(1+$BB$66)</f>
-        <v>990958.091538661</v>
+        <v>2285062.36370005</v>
       </c>
       <c r="EK52" s="51" t="n">
         <f aca="false">+EJ52*(1+$BB$66)</f>
-        <v>1000867.67245405</v>
+        <v>2330763.61097405</v>
       </c>
       <c r="EL52" s="51" t="n">
         <f aca="false">+EK52*(1+$BB$66)</f>
-        <v>1010876.34917859</v>
+        <v>2377378.88319353</v>
       </c>
       <c r="EM52" s="51" t="n">
         <f aca="false">+EL52*(1+$BB$66)</f>
-        <v>1020985.11267037</v>
+        <v>2424926.4608574</v>
       </c>
       <c r="EN52" s="51" t="n">
         <f aca="false">+EM52*(1+$BB$66)</f>
-        <v>1031194.96379708</v>
+        <v>2473424.99007455</v>
       </c>
       <c r="EO52" s="51" t="n">
         <f aca="false">+EN52*(1+$BB$66)</f>
-        <v>1041506.91343505</v>
+        <v>2522893.48987604</v>
       </c>
       <c r="EP52" s="51" t="n">
         <f aca="false">+EO52*(1+$BB$66)</f>
-        <v>1051921.9825694</v>
+        <v>2573351.35967356</v>
       </c>
       <c r="EQ52" s="51"/>
       <c r="ER52" s="51"/>
@@ -17996,39 +22248,39 @@
       </c>
       <c r="AQ53" s="35" t="n">
         <f aca="false">+AQ52/AQ$30</f>
-        <v>0.418881670159824</v>
+        <v>0.376381670159824</v>
       </c>
       <c r="AR53" s="35" t="n">
         <f aca="false">+AR52/AR$30</f>
-        <v>0.349005016498223</v>
+        <v>0.313483086673662</v>
       </c>
       <c r="AS53" s="35" t="n">
         <f aca="false">+AS52/AS$30</f>
-        <v>0.379832820114335</v>
+        <v>0.322930840608047</v>
       </c>
       <c r="AT53" s="35" t="n">
         <f aca="false">+AT52/AT$30</f>
-        <v>0.417884356782085</v>
+        <v>0.353367743193357</v>
       </c>
       <c r="AU53" s="35" t="n">
         <f aca="false">+AU52/AU$30</f>
-        <v>0.421084587300924</v>
+        <v>0.362924010355414</v>
       </c>
       <c r="AV53" s="35" t="n">
         <f aca="false">+AV52/AV$30</f>
-        <v>0.444981938859944</v>
+        <v>0.372325845089635</v>
       </c>
       <c r="AW53" s="35" t="n">
         <f aca="false">+AW52/AW$30</f>
-        <v>0.447867576789271</v>
+        <v>0.374587863322223</v>
       </c>
       <c r="AX53" s="35" t="n">
         <f aca="false">+AX52/AX$30</f>
-        <v>0.450480109700286</v>
+        <v>0.376635797686369</v>
       </c>
       <c r="AY53" s="35" t="n">
         <f aca="false">+AY52/AY$30</f>
-        <v>0.452845385032223</v>
+        <v>0.434489909691053</v>
       </c>
       <c r="AZ53" s="53"/>
       <c r="BA53" s="53"/>
@@ -18286,39 +22538,39 @@
       </c>
       <c r="AQ54" s="54" t="n">
         <f aca="false">AQ52/AQ56</f>
-        <v>59.537264221087</v>
+        <v>53.4965756217727</v>
       </c>
       <c r="AR54" s="54" t="n">
         <f aca="false">AR52/AR56</f>
-        <v>57.1214001583206</v>
+        <v>51.3075514398599</v>
       </c>
       <c r="AS54" s="54" t="n">
         <f aca="false">AS52/AS56</f>
-        <v>70.958252540065</v>
+        <v>60.3281415596042</v>
       </c>
       <c r="AT54" s="54" t="n">
         <f aca="false">AT52/AT56</f>
-        <v>88.3180284836289</v>
+        <v>74.6827247826868</v>
       </c>
       <c r="AU54" s="54" t="n">
         <f aca="false">AU52/AU56</f>
-        <v>100.680514312409</v>
+        <v>86.77443231327</v>
       </c>
       <c r="AV54" s="54" t="n">
         <f aca="false">AV52/AV56</f>
-        <v>120.365297051282</v>
+        <v>100.712202070271</v>
       </c>
       <c r="AW54" s="54" t="n">
         <f aca="false">AW52/AW56</f>
-        <v>137.05388760919</v>
+        <v>114.629246634851</v>
       </c>
       <c r="AX54" s="54" t="n">
         <f aca="false">AX52/AX56</f>
-        <v>155.955316438355</v>
+        <v>130.390562747087</v>
       </c>
       <c r="AY54" s="54" t="n">
         <f aca="false">AY52/AY56</f>
-        <v>177.360677223394</v>
+        <v>170.171602000654</v>
       </c>
       <c r="AZ54" s="54"/>
       <c r="BA54" s="54"/>
@@ -18550,48 +22802,48 @@
       </c>
       <c r="AP55" s="35" t="n">
         <f aca="false">+AP54/AO54-1</f>
-        <v>0.228442069243591</v>
+        <v>0.228442069243592</v>
       </c>
       <c r="AQ55" s="35" t="n">
         <f aca="false">+AQ54/AP54-1</f>
-        <v>0.339196023116921</v>
+        <v>0.203320345002973</v>
       </c>
       <c r="AR55" s="35" t="n">
         <f aca="false">+AR54/AQ54-1</f>
-        <v>-0.0405773441956502</v>
+        <v>-0.0409189589514934</v>
       </c>
       <c r="AS55" s="35" t="n">
         <f aca="false">+AS54/AR54-1</f>
-        <v>0.242235875580666</v>
+        <v>0.175814083241095</v>
       </c>
       <c r="AT55" s="35" t="n">
         <f aca="false">+AT54/AS54-1</f>
-        <v>0.244647737537817</v>
+        <v>0.237941744134457</v>
       </c>
       <c r="AU55" s="35" t="n">
         <f aca="false">+AU54/AT54-1</f>
-        <v>0.13997692250424</v>
+        <v>0.161907691045926</v>
       </c>
       <c r="AV55" s="35" t="n">
         <f aca="false">+AV54/AU54-1</f>
-        <v>0.195517304150747</v>
+        <v>0.1606206965052</v>
       </c>
       <c r="AW55" s="35" t="n">
         <f aca="false">+AW54/AV54-1</f>
-        <v>0.138649519145023</v>
+        <v>0.138186280098119</v>
       </c>
       <c r="AX55" s="35" t="n">
         <f aca="false">+AX54/AW54-1</f>
-        <v>0.137912387301716</v>
+        <v>0.137498209008064</v>
       </c>
       <c r="AY55" s="35" t="n">
         <f aca="false">+AY54/AX54-1</f>
-        <v>0.137253165033978</v>
+        <v>0.305091399373195</v>
       </c>
       <c r="AZ55" s="53"/>
       <c r="BA55" s="35" t="n">
         <f aca="false">+(AY54/AO54)^(1/(AY2-AO2))-1</f>
-        <v>0.172267512979926</v>
+        <v>0.167426922302654</v>
       </c>
       <c r="BB55" s="53"/>
       <c r="BC55" s="53"/>
@@ -20602,7 +24854,7 @@
         <v>180</v>
       </c>
       <c r="BB66" s="61" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="BC66" s="57"/>
       <c r="BD66" s="58" t="s">
@@ -20850,46 +25102,46 @@
       </c>
       <c r="AQ67" s="58" t="n">
         <f aca="false">AQ44/AQ30</f>
-        <v>0.48</v>
+        <v>0.43</v>
       </c>
       <c r="AR67" s="58" t="n">
         <f aca="false">AR44/AR30</f>
-        <v>0.48</v>
+        <v>0.43</v>
       </c>
       <c r="AS67" s="58" t="n">
         <f aca="false">AS44/AS30</f>
-        <v>0.52</v>
+        <v>0.439999999999999</v>
       </c>
       <c r="AT67" s="58" t="n">
         <f aca="false">AT44/AT30</f>
-        <v>0.569999999999999</v>
+        <v>0.48</v>
       </c>
       <c r="AU67" s="58" t="n">
         <f aca="false">AU44/AU30</f>
-        <v>0.57</v>
+        <v>0.49</v>
       </c>
       <c r="AV67" s="58" t="n">
         <f aca="false">AV44/AV30</f>
-        <v>0.600000000000001</v>
+        <v>0.500000000000001</v>
       </c>
       <c r="AW67" s="58" t="n">
         <f aca="false">AW44/AW30</f>
-        <v>0.600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AX67" s="58" t="n">
         <f aca="false">AX44/AX30</f>
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AY67" s="58" t="n">
         <f aca="false">AY44/AY30</f>
-        <v>0.600000000000001</v>
+        <v>0.580000000000001</v>
       </c>
       <c r="BA67" s="63" t="s">
         <v>183</v>
       </c>
       <c r="BB67" s="64" t="n">
         <f aca="false">+Main!E12</f>
-        <v>0.112193487547429</v>
+        <v>0.108897277026286</v>
       </c>
       <c r="BD67" s="58" t="s">
         <v>184</v>
@@ -21045,39 +25297,39 @@
       </c>
       <c r="AQ68" s="58" t="n">
         <f aca="false">AQ52/AQ30</f>
-        <v>0.418881670159824</v>
+        <v>0.376381670159824</v>
       </c>
       <c r="AR68" s="58" t="n">
         <f aca="false">AR52/AR30</f>
-        <v>0.349005016498223</v>
+        <v>0.313483086673662</v>
       </c>
       <c r="AS68" s="58" t="n">
         <f aca="false">AS52/AS30</f>
-        <v>0.379832820114335</v>
+        <v>0.322930840608047</v>
       </c>
       <c r="AT68" s="58" t="n">
         <f aca="false">AT52/AT30</f>
-        <v>0.417884356782085</v>
+        <v>0.353367743193357</v>
       </c>
       <c r="AU68" s="58" t="n">
         <f aca="false">AU52/AU30</f>
-        <v>0.421084587300924</v>
+        <v>0.362924010355414</v>
       </c>
       <c r="AV68" s="58" t="n">
         <f aca="false">AV52/AV30</f>
-        <v>0.444981938859944</v>
+        <v>0.372325845089635</v>
       </c>
       <c r="AW68" s="58" t="n">
         <f aca="false">AW52/AW30</f>
-        <v>0.447867576789271</v>
+        <v>0.374587863322223</v>
       </c>
       <c r="AX68" s="58" t="n">
         <f aca="false">AX52/AX30</f>
-        <v>0.450480109700286</v>
+        <v>0.376635797686369</v>
       </c>
       <c r="AY68" s="58" t="n">
         <f aca="false">AY52/AY30</f>
-        <v>0.452845385032223</v>
+        <v>0.434489909691053</v>
       </c>
       <c r="BA68" s="65" t="s">
         <v>186</v>
@@ -21092,11 +25344,20 @@
         <f aca="false">+(SUM(T173:W173)+SUM(T174:W174)-SUM(T175:W175))/(Main!B17-0.1)</f>
         <v>1768267.65676568</v>
       </c>
-      <c r="BF68" s="67"/>
+      <c r="BF68" s="68" t="s">
+        <v>3</v>
+      </c>
+      <c r="BG68" s="57" t="s">
+        <v>188</v>
+      </c>
+      <c r="BH68" s="57" t="n">
+        <f aca="false">+BE68/Main!F7-1</f>
+        <v>0.181655338703697</v>
+      </c>
     </row>
     <row r="69" s="58" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="58" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B69" s="58" t="n">
         <f aca="false">B50/B48</f>
@@ -21275,202 +25536,202 @@
         <v>0.3</v>
       </c>
       <c r="BA69" s="63" t="s">
-        <v>189</v>
-      </c>
-      <c r="BB69" s="68" t="n">
+        <v>190</v>
+      </c>
+      <c r="BB69" s="69" t="n">
         <f aca="false">NPV(BB67,AO52:EP52)+Main!F5-Main!F6</f>
-        <v>2462671.65235141</v>
+        <v>2536851.39279</v>
       </c>
       <c r="BD69" s="58" t="s">
-        <v>190</v>
-      </c>
-      <c r="BE69" s="69" t="n">
+        <v>191</v>
+      </c>
+      <c r="BE69" s="70" t="n">
         <f aca="false">+(BE67*(1+0.1))/(Main!B17-0.1)</f>
         <v>23.1146098923618</v>
       </c>
     </row>
     <row r="70" s="58" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="70" t="s">
-        <v>191</v>
-      </c>
-      <c r="B70" s="70"/>
-      <c r="C70" s="70"/>
-      <c r="D70" s="70"/>
-      <c r="E70" s="70"/>
-      <c r="F70" s="70" t="n">
+      <c r="A70" s="71" t="s">
+        <v>192</v>
+      </c>
+      <c r="B70" s="71"/>
+      <c r="C70" s="71"/>
+      <c r="D70" s="71"/>
+      <c r="E70" s="71"/>
+      <c r="F70" s="71" t="n">
         <f aca="false">+F31+F67</f>
         <v>0.278703537866846</v>
       </c>
-      <c r="G70" s="70" t="n">
+      <c r="G70" s="71" t="n">
         <f aca="false">+G31+G67</f>
         <v>0.403737469989678</v>
       </c>
-      <c r="H70" s="70" t="n">
+      <c r="H70" s="71" t="n">
         <f aca="false">+H31+H67</f>
         <v>0.634708893094559</v>
       </c>
-      <c r="I70" s="70" t="n">
+      <c r="I70" s="71" t="n">
         <f aca="false">+I31+I67</f>
         <v>0.655505212116122</v>
       </c>
-      <c r="J70" s="70" t="n">
+      <c r="J70" s="71" t="n">
         <f aca="false">+J31+J67</f>
         <v>0.651690586904678</v>
       </c>
-      <c r="K70" s="70" t="n">
+      <c r="K70" s="71" t="n">
         <f aca="false">+K31+K67</f>
         <v>0.60100741835444</v>
       </c>
-      <c r="L70" s="70" t="n">
+      <c r="L70" s="71" t="n">
         <f aca="false">+L31+L67</f>
         <v>0.616145458642776</v>
       </c>
-      <c r="M70" s="70" t="n">
+      <c r="M70" s="71" t="n">
         <f aca="false">+M31+M67</f>
         <v>0.689175171945284</v>
       </c>
-      <c r="N70" s="70" t="n">
+      <c r="N70" s="71" t="n">
         <f aca="false">+N31+N67</f>
         <v>0.575593203899186</v>
       </c>
-      <c r="O70" s="70" t="n">
+      <c r="O70" s="71" t="n">
         <f aca="false">+O31+O67</f>
         <v>0.646336902203305</v>
       </c>
-      <c r="P70" s="70" t="n">
+      <c r="P70" s="71" t="n">
         <f aca="false">+P31+P67</f>
         <v>0.663205754709235</v>
       </c>
-      <c r="Q70" s="70" t="n">
+      <c r="Q70" s="71" t="n">
         <f aca="false">+Q31+Q67</f>
         <v>0.650995763498262</v>
       </c>
-      <c r="R70" s="70" t="n">
+      <c r="R70" s="71" t="n">
         <f aca="false">+R31+R67</f>
         <v>0.736961725635971</v>
       </c>
-      <c r="S70" s="70" t="n">
+      <c r="S70" s="71" t="n">
         <f aca="false">+S31+S67</f>
         <v>0.588384296083295</v>
       </c>
-      <c r="T70" s="70"/>
-      <c r="U70" s="70"/>
-      <c r="V70" s="70"/>
-      <c r="W70" s="70"/>
-      <c r="X70" s="70"/>
-      <c r="Y70" s="70"/>
-      <c r="Z70" s="70" t="n">
+      <c r="T70" s="71"/>
+      <c r="U70" s="71"/>
+      <c r="V70" s="71"/>
+      <c r="W70" s="71"/>
+      <c r="X70" s="71"/>
+      <c r="Y70" s="71"/>
+      <c r="Z70" s="71" t="n">
         <f aca="false">+Z31+Z67</f>
         <v>0.473187819994611</v>
       </c>
-      <c r="AA70" s="70" t="n">
+      <c r="AA70" s="71" t="n">
         <f aca="false">+AA31+AA67</f>
         <v>0.47704669864819</v>
       </c>
-      <c r="AB70" s="70" t="n">
+      <c r="AB70" s="71" t="n">
         <f aca="false">+AB31+AB67</f>
         <v>0.903064975948443</v>
       </c>
-      <c r="AC70" s="70" t="n">
+      <c r="AC70" s="71" t="n">
         <f aca="false">+AC31+AC67</f>
         <v>0.98419705664448</v>
       </c>
-      <c r="AD70" s="70" t="n">
+      <c r="AD70" s="71" t="n">
         <f aca="false">+AD31+AD67</f>
         <v>0.785373995044298</v>
       </c>
-      <c r="AE70" s="70" t="n">
+      <c r="AE70" s="71" t="n">
         <f aca="false">+AE31+AE67</f>
         <v>0.991245449107943</v>
       </c>
-      <c r="AF70" s="70" t="n">
+      <c r="AF70" s="71" t="n">
         <f aca="false">+AF31+AF67</f>
         <v>0.967871711012133</v>
       </c>
-      <c r="AG70" s="70" t="n">
+      <c r="AG70" s="71" t="n">
         <f aca="false">+AG31+AG67</f>
         <v>0.819692862580288</v>
       </c>
-      <c r="AH70" s="70" t="n">
+      <c r="AH70" s="71" t="n">
         <f aca="false">+AH31+AH67</f>
         <v>0.605387995765666</v>
       </c>
-      <c r="AI70" s="70" t="n">
+      <c r="AI70" s="71" t="n">
         <f aca="false">+AI31+AI67</f>
         <v>0.596013922644348</v>
       </c>
-      <c r="AJ70" s="70" t="n">
+      <c r="AJ70" s="71" t="n">
         <f aca="false">+AJ31+AJ67</f>
         <v>0.768276149635538</v>
       </c>
-      <c r="AK70" s="70" t="n">
+      <c r="AK70" s="71" t="n">
         <f aca="false">+AK31+AK67</f>
         <v>0.237020941708893</v>
       </c>
-      <c r="AL70" s="70" t="n">
+      <c r="AL70" s="71" t="n">
         <f aca="false">+AL31+AL67</f>
         <v>0.503429960936429</v>
       </c>
-      <c r="AM70" s="70" t="n">
+      <c r="AM70" s="71" t="n">
         <f aca="false">+AM31+AM67</f>
         <v>0.641171482118562</v>
       </c>
-      <c r="AN70" s="70" t="n">
+      <c r="AN70" s="71" t="n">
         <f aca="false">+AN31+AN67</f>
         <v>0.636048936578254</v>
       </c>
-      <c r="AO70" s="70" t="n">
+      <c r="AO70" s="71" t="n">
         <f aca="false">+AO31+AO67</f>
         <v>0.7</v>
       </c>
-      <c r="AP70" s="70" t="n">
+      <c r="AP70" s="71" t="n">
         <f aca="false">+AP31+AP67</f>
         <v>0.62</v>
       </c>
-      <c r="AQ70" s="70" t="n">
+      <c r="AQ70" s="71" t="n">
         <f aca="false">+AQ31+AQ67</f>
-        <v>0.63</v>
-      </c>
-      <c r="AR70" s="70" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="AR70" s="71" t="n">
         <f aca="false">+AR31+AR67</f>
+        <v>0.57</v>
+      </c>
+      <c r="AS70" s="71" t="n">
+        <f aca="false">+AS31+AS67</f>
+        <v>0.569999999999999</v>
+      </c>
+      <c r="AT70" s="71" t="n">
+        <f aca="false">+AT31+AT67</f>
+        <v>0.599999999999999</v>
+      </c>
+      <c r="AU70" s="71" t="n">
+        <f aca="false">+AU31+AU67</f>
+        <v>0.61</v>
+      </c>
+      <c r="AV70" s="71" t="n">
+        <f aca="false">+AV31+AV67</f>
+        <v>0.620000000000001</v>
+      </c>
+      <c r="AW70" s="71" t="n">
+        <f aca="false">+AW31+AW67</f>
         <v>0.62</v>
       </c>
-      <c r="AS70" s="70" t="n">
-        <f aca="false">+AS31+AS67</f>
-        <v>0.65</v>
-      </c>
-      <c r="AT70" s="70" t="n">
-        <f aca="false">+AT31+AT67</f>
-        <v>0.689999999999999</v>
-      </c>
-      <c r="AU70" s="70" t="n">
-        <f aca="false">+AU31+AU67</f>
-        <v>0.69</v>
-      </c>
-      <c r="AV70" s="70" t="n">
-        <f aca="false">+AV31+AV67</f>
-        <v>0.720000000000001</v>
-      </c>
-      <c r="AW70" s="70" t="n">
-        <f aca="false">+AW31+AW67</f>
-        <v>0.720000000000001</v>
-      </c>
-      <c r="AX70" s="70" t="n">
+      <c r="AX70" s="71" t="n">
         <f aca="false">+AX31+AX67</f>
-        <v>0.72</v>
-      </c>
-      <c r="AY70" s="70" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="AY70" s="71" t="n">
         <f aca="false">+AY31+AY67</f>
-        <v>0.720000000000001</v>
+        <v>0.700000000000001</v>
       </c>
       <c r="BA70" s="65" t="s">
-        <v>192</v>
-      </c>
-      <c r="BB70" s="71" t="n">
+        <v>193</v>
+      </c>
+      <c r="BB70" s="72" t="n">
         <f aca="false">+BB69/Main!F1</f>
-        <v>1116.79280472783</v>
-      </c>
-      <c r="BE70" s="69"/>
+        <v>1150.43244982599</v>
+      </c>
+      <c r="BE70" s="70"/>
     </row>
     <row r="71" s="58" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="58" t="s">
@@ -21601,49 +25862,49 @@
       </c>
       <c r="AQ71" s="58" t="n">
         <f aca="false">+(AQ44-AP44)/(AQ30-AP30)</f>
-        <v>0.88</v>
+        <v>0.496666666666667</v>
       </c>
       <c r="AR71" s="58" t="n">
         <f aca="false">+(AR44-AQ44)/(AR30-AQ30)</f>
-        <v>0.48</v>
+        <v>0.43</v>
       </c>
       <c r="AS71" s="58" t="n">
         <f aca="false">+(AS44-AR44)/(AS30-AR30)</f>
-        <v>0.827692307692303</v>
+        <v>0.516923076923072</v>
       </c>
       <c r="AT71" s="58" t="n">
         <f aca="false">+(AT44-AS44)/(AT30-AS30)</f>
-        <v>0.986666666666663</v>
+        <v>0.813333333333331</v>
       </c>
       <c r="AU71" s="58" t="n">
         <f aca="false">+(AU44-AT44)/(AU30-AT30)</f>
-        <v>0.570000000000003</v>
+        <v>0.573333333333336</v>
       </c>
       <c r="AV71" s="58" t="n">
         <f aca="false">+(AV44-AU44)/(AV30-AU30)</f>
-        <v>0.850000000000014</v>
+        <v>0.583333333333346</v>
       </c>
       <c r="AW71" s="58" t="n">
         <f aca="false">+(AW44-AV44)/(AW30-AV30)</f>
-        <v>0.599999999999996</v>
+        <v>0.499999999999995</v>
       </c>
       <c r="AX71" s="58" t="n">
         <f aca="false">+(AX44-AW44)/(AX30-AW30)</f>
-        <v>0.599999999999996</v>
+        <v>0.499999999999997</v>
       </c>
       <c r="AY71" s="58" t="n">
         <f aca="false">+(AY44-AX44)/(AY30-AX30)</f>
-        <v>0.600000000000005</v>
-      </c>
-      <c r="AZ71" s="70"/>
-      <c r="BA71" s="72" t="s">
-        <v>193</v>
-      </c>
-      <c r="BB71" s="73" t="n">
+        <v>1.24666666666667</v>
+      </c>
+      <c r="AZ71" s="71"/>
+      <c r="BA71" s="73" t="s">
+        <v>188</v>
+      </c>
+      <c r="BB71" s="74" t="n">
         <f aca="false">+BB70/Main!F3-1</f>
-        <v>0.892869160555646</v>
-      </c>
-      <c r="BC71" s="70"/>
+        <v>0.949885508179639</v>
+      </c>
+      <c r="BC71" s="71"/>
       <c r="BD71" s="62" t="s">
         <v>194</v>
       </c>
@@ -21750,7 +26011,7 @@
       </c>
       <c r="BB72" s="67" t="n">
         <f aca="false">+BB70*(Main!F1+Main!F2)</f>
-        <v>2845036.62207936</v>
+        <v>2930733.8273737</v>
       </c>
       <c r="BD72" s="58" t="s">
         <v>195</v>
@@ -23418,7 +27679,7 @@
       <c r="EQ81" s="58"/>
       <c r="ER81" s="58"/>
     </row>
-    <row r="82" s="74" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="82" s="75" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="58" t="s">
         <v>203</v>
       </c>
@@ -23813,256 +28074,256 @@
       <c r="EQ83" s="40"/>
       <c r="ER83" s="40"/>
     </row>
-    <row r="84" s="76" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="74" t="s">
+    <row r="84" s="77" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="75" t="s">
         <v>204</v>
       </c>
-      <c r="B84" s="74" t="n">
+      <c r="B84" s="75" t="n">
         <f aca="false">+B124/B56</f>
         <v>44.9409190371991</v>
       </c>
-      <c r="C84" s="74" t="n">
+      <c r="C84" s="75" t="n">
         <f aca="false">+C124/C56</f>
         <v>46.3571691854036</v>
       </c>
-      <c r="D84" s="74" t="n">
+      <c r="D84" s="75" t="n">
         <f aca="false">+D124/D56</f>
         <v>46.1831038332713</v>
       </c>
-      <c r="E84" s="74" t="n">
+      <c r="E84" s="75" t="n">
         <f aca="false">+E124/E56</f>
         <v>47.6185606060606</v>
       </c>
-      <c r="F84" s="74" t="n">
+      <c r="F84" s="75" t="n">
         <f aca="false">+F124/F56</f>
         <v>48.0720338983051</v>
       </c>
-      <c r="G84" s="74" t="n">
+      <c r="G84" s="75" t="n">
         <f aca="false">+G124/G56</f>
         <v>51.3143185298622</v>
       </c>
-      <c r="H84" s="74" t="n">
+      <c r="H84" s="75" t="n">
         <f aca="false">+H124/H56</f>
         <v>54.0980689132904</v>
       </c>
-      <c r="I84" s="74" t="n">
+      <c r="I84" s="75" t="n">
         <f aca="false">+I124/I56</f>
         <v>58.238783269962</v>
       </c>
-      <c r="J84" s="74" t="n">
+      <c r="J84" s="75" t="n">
         <f aca="false">+J124/J56</f>
         <v>56.9634285714286</v>
       </c>
-      <c r="K84" s="74" t="n">
+      <c r="K84" s="75" t="n">
         <f aca="false">+K124/K56</f>
         <v>60.0624521072797</v>
       </c>
-      <c r="L84" s="74" t="n">
+      <c r="L84" s="75" t="n">
         <f aca="false">+L124/L56</f>
         <v>63.2803846153846</v>
       </c>
-      <c r="M84" s="74" t="n">
+      <c r="M84" s="75" t="n">
         <f aca="false">+M124/M56</f>
         <v>70.2720277029627</v>
       </c>
-      <c r="N84" s="74" t="n">
+      <c r="N84" s="75" t="n">
         <f aca="false">+N124/N56</f>
         <v>71.4397683397683</v>
       </c>
-      <c r="O84" s="74" t="n">
+      <c r="O84" s="75" t="n">
         <f aca="false">+O124/O56</f>
         <v>75.9027237354086</v>
       </c>
-      <c r="P84" s="74" t="n">
+      <c r="P84" s="75" t="n">
         <f aca="false">+P124/P56</f>
         <v>75.4533437013997</v>
       </c>
-      <c r="Q84" s="74" t="n">
+      <c r="Q84" s="75" t="n">
         <f aca="false">+Q124/Q56</f>
         <v>84.695126705653</v>
       </c>
-      <c r="R84" s="74" t="n">
+      <c r="R84" s="75" t="n">
         <f aca="false">+R124/R56</f>
         <v>95.039391575663</v>
       </c>
-      <c r="S84" s="74" t="n">
+      <c r="S84" s="75" t="n">
         <f aca="false">+S124/S56</f>
         <v>101.800857365549</v>
       </c>
-      <c r="T84" s="74"/>
-      <c r="U84" s="74"/>
-      <c r="V84" s="74"/>
-      <c r="W84" s="74"/>
-      <c r="X84" s="74"/>
-      <c r="Y84" s="74"/>
-      <c r="Z84" s="74" t="n">
+      <c r="T84" s="75"/>
+      <c r="U84" s="75"/>
+      <c r="V84" s="75"/>
+      <c r="W84" s="75"/>
+      <c r="X84" s="75"/>
+      <c r="Y84" s="75"/>
+      <c r="Z84" s="75" t="n">
         <f aca="false">+Z124/Z56</f>
         <v>2.84084880636605</v>
       </c>
-      <c r="AA84" s="74" t="n">
+      <c r="AA84" s="75" t="n">
         <f aca="false">+AA124/AA56</f>
         <v>5.42705447830102</v>
       </c>
-      <c r="AB84" s="74" t="n">
+      <c r="AB84" s="75" t="n">
         <f aca="false">+AB124/AB56</f>
         <v>6.14620580055622</v>
       </c>
-      <c r="AC84" s="74" t="n">
+      <c r="AC84" s="75" t="n">
         <f aca="false">+AC124/AC56</f>
         <v>13.5495495495496</v>
       </c>
-      <c r="AD84" s="74" t="n">
+      <c r="AD84" s="75" t="n">
         <f aca="false">+AD124/AD56</f>
         <v>15.4987732211707</v>
       </c>
-      <c r="AE84" s="74" t="n">
+      <c r="AE84" s="75" t="n">
         <f aca="false">+AE124/AE56</f>
         <v>20.237264957265</v>
       </c>
-      <c r="AF84" s="74" t="n">
+      <c r="AF84" s="75" t="n">
         <f aca="false">+AF124/AF56</f>
         <v>25.1512178619756</v>
       </c>
-      <c r="AG84" s="74" t="n">
+      <c r="AG84" s="75" t="n">
         <f aca="false">+AG124/AG56</f>
         <v>28.8007531667237</v>
       </c>
-      <c r="AH84" s="74" t="n">
+      <c r="AH84" s="75" t="n">
         <f aca="false">+AH124/AH56</f>
         <v>35.1369958275383</v>
       </c>
-      <c r="AI84" s="74" t="n">
+      <c r="AI84" s="75" t="n">
         <f aca="false">+AI124/AI56</f>
         <v>44.4217451523546</v>
       </c>
-      <c r="AJ84" s="74" t="n">
+      <c r="AJ84" s="75" t="n">
         <f aca="false">+AJ124/AJ56</f>
         <v>43.6792584819867</v>
       </c>
-      <c r="AK84" s="74" t="n">
+      <c r="AK84" s="75" t="n">
         <f aca="false">+AK124/AK56</f>
         <v>46.5259067357513</v>
       </c>
-      <c r="AL84" s="74" t="n">
+      <c r="AL84" s="75" t="n">
         <f aca="false">+AL124/AL56</f>
         <v>58.2609357170027</v>
       </c>
-      <c r="AM84" s="74" t="n">
+      <c r="AM84" s="75" t="n">
         <f aca="false">+AM124/AM56</f>
         <v>69.8687834736037</v>
       </c>
-      <c r="AN84" s="74" t="n">
+      <c r="AN84" s="75" t="n">
         <f aca="false">+AN124/AN56</f>
         <v>84.3989898989899</v>
       </c>
-      <c r="AO84" s="74"/>
-      <c r="AP84" s="74"/>
-      <c r="AQ84" s="74"/>
-      <c r="AR84" s="75"/>
-      <c r="AS84" s="74"/>
-      <c r="AT84" s="74"/>
-      <c r="AU84" s="74"/>
-      <c r="AV84" s="74"/>
-      <c r="AW84" s="74"/>
-      <c r="AX84" s="74"/>
-      <c r="AY84" s="74"/>
-      <c r="AZ84" s="74"/>
-      <c r="BA84" s="74"/>
-      <c r="BB84" s="74"/>
-      <c r="BC84" s="74"/>
-      <c r="BD84" s="74"/>
-      <c r="BE84" s="74"/>
-      <c r="BF84" s="74"/>
-      <c r="BG84" s="74"/>
-      <c r="BH84" s="74"/>
-      <c r="BI84" s="74"/>
-      <c r="BJ84" s="74"/>
-      <c r="BK84" s="74"/>
-      <c r="BL84" s="74"/>
-      <c r="BM84" s="74"/>
-      <c r="BN84" s="74"/>
-      <c r="BO84" s="74"/>
-      <c r="BP84" s="74"/>
-      <c r="BQ84" s="74"/>
-      <c r="BR84" s="74"/>
-      <c r="BS84" s="74"/>
-      <c r="BT84" s="74"/>
-      <c r="BU84" s="74"/>
-      <c r="BV84" s="74"/>
-      <c r="BW84" s="74"/>
-      <c r="BX84" s="74"/>
-      <c r="BY84" s="74"/>
-      <c r="BZ84" s="74"/>
-      <c r="CA84" s="74"/>
-      <c r="CB84" s="74"/>
-      <c r="CC84" s="74"/>
-      <c r="CD84" s="74"/>
-      <c r="CE84" s="74"/>
-      <c r="CF84" s="74"/>
-      <c r="CG84" s="74"/>
-      <c r="CH84" s="74"/>
-      <c r="CI84" s="74"/>
-      <c r="CJ84" s="74"/>
-      <c r="CK84" s="74"/>
-      <c r="CL84" s="74"/>
-      <c r="CM84" s="74"/>
-      <c r="CN84" s="74"/>
-      <c r="CO84" s="74"/>
-      <c r="CP84" s="74"/>
-      <c r="CQ84" s="74"/>
-      <c r="CR84" s="74"/>
-      <c r="CS84" s="74"/>
-      <c r="CT84" s="74"/>
-      <c r="CU84" s="74"/>
-      <c r="CV84" s="74"/>
-      <c r="CW84" s="74"/>
-      <c r="CX84" s="74"/>
-      <c r="CY84" s="74"/>
-      <c r="CZ84" s="74"/>
-      <c r="DA84" s="74"/>
-      <c r="DB84" s="74"/>
-      <c r="DC84" s="74"/>
-      <c r="DD84" s="74"/>
-      <c r="DE84" s="74"/>
-      <c r="DF84" s="74"/>
-      <c r="DG84" s="74"/>
-      <c r="DH84" s="74"/>
-      <c r="DI84" s="74"/>
-      <c r="DJ84" s="74"/>
-      <c r="DK84" s="74"/>
-      <c r="DL84" s="74"/>
-      <c r="DM84" s="74"/>
-      <c r="DN84" s="74"/>
-      <c r="DO84" s="74"/>
-      <c r="DP84" s="74"/>
-      <c r="DQ84" s="74"/>
-      <c r="DR84" s="74"/>
-      <c r="DS84" s="74"/>
-      <c r="DT84" s="74"/>
-      <c r="DU84" s="74"/>
-      <c r="DV84" s="74"/>
-      <c r="DW84" s="74"/>
-      <c r="DX84" s="74"/>
-      <c r="DY84" s="74"/>
-      <c r="DZ84" s="74"/>
-      <c r="EA84" s="74"/>
-      <c r="EB84" s="74"/>
-      <c r="EC84" s="74"/>
-      <c r="ED84" s="74"/>
-      <c r="EE84" s="74"/>
-      <c r="EF84" s="74"/>
-      <c r="EG84" s="74"/>
-      <c r="EH84" s="74"/>
-      <c r="EI84" s="74"/>
-      <c r="EJ84" s="74"/>
-      <c r="EK84" s="74"/>
-      <c r="EL84" s="74"/>
-      <c r="EM84" s="74"/>
-      <c r="EN84" s="74"/>
-      <c r="EO84" s="74"/>
-      <c r="EP84" s="74"/>
-      <c r="EQ84" s="74"/>
-      <c r="ER84" s="74"/>
+      <c r="AO84" s="75"/>
+      <c r="AP84" s="75"/>
+      <c r="AQ84" s="75"/>
+      <c r="AR84" s="76"/>
+      <c r="AS84" s="75"/>
+      <c r="AT84" s="75"/>
+      <c r="AU84" s="75"/>
+      <c r="AV84" s="75"/>
+      <c r="AW84" s="75"/>
+      <c r="AX84" s="75"/>
+      <c r="AY84" s="75"/>
+      <c r="AZ84" s="75"/>
+      <c r="BA84" s="75"/>
+      <c r="BB84" s="75"/>
+      <c r="BC84" s="75"/>
+      <c r="BD84" s="75"/>
+      <c r="BE84" s="75"/>
+      <c r="BF84" s="75"/>
+      <c r="BG84" s="75"/>
+      <c r="BH84" s="75"/>
+      <c r="BI84" s="75"/>
+      <c r="BJ84" s="75"/>
+      <c r="BK84" s="75"/>
+      <c r="BL84" s="75"/>
+      <c r="BM84" s="75"/>
+      <c r="BN84" s="75"/>
+      <c r="BO84" s="75"/>
+      <c r="BP84" s="75"/>
+      <c r="BQ84" s="75"/>
+      <c r="BR84" s="75"/>
+      <c r="BS84" s="75"/>
+      <c r="BT84" s="75"/>
+      <c r="BU84" s="75"/>
+      <c r="BV84" s="75"/>
+      <c r="BW84" s="75"/>
+      <c r="BX84" s="75"/>
+      <c r="BY84" s="75"/>
+      <c r="BZ84" s="75"/>
+      <c r="CA84" s="75"/>
+      <c r="CB84" s="75"/>
+      <c r="CC84" s="75"/>
+      <c r="CD84" s="75"/>
+      <c r="CE84" s="75"/>
+      <c r="CF84" s="75"/>
+      <c r="CG84" s="75"/>
+      <c r="CH84" s="75"/>
+      <c r="CI84" s="75"/>
+      <c r="CJ84" s="75"/>
+      <c r="CK84" s="75"/>
+      <c r="CL84" s="75"/>
+      <c r="CM84" s="75"/>
+      <c r="CN84" s="75"/>
+      <c r="CO84" s="75"/>
+      <c r="CP84" s="75"/>
+      <c r="CQ84" s="75"/>
+      <c r="CR84" s="75"/>
+      <c r="CS84" s="75"/>
+      <c r="CT84" s="75"/>
+      <c r="CU84" s="75"/>
+      <c r="CV84" s="75"/>
+      <c r="CW84" s="75"/>
+      <c r="CX84" s="75"/>
+      <c r="CY84" s="75"/>
+      <c r="CZ84" s="75"/>
+      <c r="DA84" s="75"/>
+      <c r="DB84" s="75"/>
+      <c r="DC84" s="75"/>
+      <c r="DD84" s="75"/>
+      <c r="DE84" s="75"/>
+      <c r="DF84" s="75"/>
+      <c r="DG84" s="75"/>
+      <c r="DH84" s="75"/>
+      <c r="DI84" s="75"/>
+      <c r="DJ84" s="75"/>
+      <c r="DK84" s="75"/>
+      <c r="DL84" s="75"/>
+      <c r="DM84" s="75"/>
+      <c r="DN84" s="75"/>
+      <c r="DO84" s="75"/>
+      <c r="DP84" s="75"/>
+      <c r="DQ84" s="75"/>
+      <c r="DR84" s="75"/>
+      <c r="DS84" s="75"/>
+      <c r="DT84" s="75"/>
+      <c r="DU84" s="75"/>
+      <c r="DV84" s="75"/>
+      <c r="DW84" s="75"/>
+      <c r="DX84" s="75"/>
+      <c r="DY84" s="75"/>
+      <c r="DZ84" s="75"/>
+      <c r="EA84" s="75"/>
+      <c r="EB84" s="75"/>
+      <c r="EC84" s="75"/>
+      <c r="ED84" s="75"/>
+      <c r="EE84" s="75"/>
+      <c r="EF84" s="75"/>
+      <c r="EG84" s="75"/>
+      <c r="EH84" s="75"/>
+      <c r="EI84" s="75"/>
+      <c r="EJ84" s="75"/>
+      <c r="EK84" s="75"/>
+      <c r="EL84" s="75"/>
+      <c r="EM84" s="75"/>
+      <c r="EN84" s="75"/>
+      <c r="EO84" s="75"/>
+      <c r="EP84" s="75"/>
+      <c r="EQ84" s="75"/>
+      <c r="ER84" s="75"/>
     </row>
     <row r="85" s="39" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="58" t="s">
@@ -24310,249 +28571,249 @@
       <c r="ER85" s="40"/>
     </row>
     <row r="86" s="39" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="76" t="s">
+      <c r="A86" s="77" t="s">
         <v>206</v>
       </c>
-      <c r="B86" s="76"/>
-      <c r="C86" s="76" t="n">
+      <c r="B86" s="77"/>
+      <c r="C86" s="77" t="n">
         <f aca="false">+(C52-B52)/(C105-B105)</f>
         <v>-0.12953712953713</v>
       </c>
-      <c r="D86" s="76" t="n">
+      <c r="D86" s="77" t="n">
         <f aca="false">+(D52-C52)/(D105-C105)</f>
         <v>-0.372682926829268</v>
       </c>
-      <c r="E86" s="76" t="n">
+      <c r="E86" s="77" t="n">
         <f aca="false">+(E52-D52)/(E105-D105)</f>
         <v>0.0444636678200692</v>
       </c>
-      <c r="F86" s="76" t="n">
+      <c r="F86" s="77" t="n">
         <f aca="false">+(F52-E52)/(F105-E105)</f>
         <v>0.227899956877965</v>
       </c>
-      <c r="G86" s="76" t="n">
+      <c r="G86" s="77" t="n">
         <f aca="false">+(G52-F52)/(G105-F105)</f>
         <v>0.548114948589507</v>
       </c>
-      <c r="H86" s="76" t="n">
+      <c r="H86" s="77" t="n">
         <f aca="false">+(H52-G52)/(H105-G105)</f>
         <v>0.992675908972012</v>
       </c>
-      <c r="I86" s="76" t="n">
+      <c r="I86" s="77" t="n">
         <f aca="false">+(I52-H52)/(I105-H105)</f>
         <v>0.505503634475597</v>
       </c>
-      <c r="J86" s="76" t="n">
+      <c r="J86" s="77" t="n">
         <f aca="false">+(J52-I52)/(J105-I105)</f>
         <v>-0.710038776389487</v>
       </c>
-      <c r="K86" s="76" t="n">
+      <c r="K86" s="77" t="n">
         <f aca="false">+(K52-J52)/(K105-J105)</f>
         <v>0.270550481362627</v>
       </c>
-      <c r="L86" s="76" t="n">
+      <c r="L86" s="77" t="n">
         <f aca="false">+(L52-K52)/(L105-K105)</f>
         <v>0.241551667934369</v>
       </c>
-      <c r="M86" s="76" t="n">
+      <c r="M86" s="77" t="n">
         <f aca="false">+(M52-L52)/(M105-L105)</f>
         <v>0.560757839721254</v>
       </c>
-      <c r="N86" s="76" t="n">
+      <c r="N86" s="77" t="n">
         <f aca="false">+(N52-M52)/(N105-M105)</f>
         <v>-0.343179772522707</v>
       </c>
-      <c r="O86" s="76" t="n">
+      <c r="O86" s="77" t="n">
         <f aca="false">+(O52-N52)/(O105-N105)</f>
         <v>0.151128266033254</v>
       </c>
-      <c r="P86" s="76" t="n">
+      <c r="P86" s="77" t="n">
         <f aca="false">+(P52-O52)/(P105-O105)</f>
         <v>-0.0752021767062202</v>
       </c>
-      <c r="Q86" s="76" t="n">
+      <c r="Q86" s="77" t="n">
         <f aca="false">+(Q52-P52)/(Q105-P105)</f>
         <v>0.315127092374458</v>
       </c>
-      <c r="R86" s="76" t="n">
+      <c r="R86" s="77" t="n">
         <f aca="false">+(R52-Q52)/(R105-Q105)</f>
         <v>0.276501959077057</v>
       </c>
-      <c r="S86" s="76" t="n">
+      <c r="S86" s="77" t="n">
         <f aca="false">+(S52-R52)/(S105-R105)</f>
         <v>-0.387779501098617</v>
       </c>
-      <c r="T86" s="76"/>
-      <c r="U86" s="76"/>
-      <c r="V86" s="76"/>
-      <c r="W86" s="76"/>
-      <c r="X86" s="76"/>
-      <c r="Y86" s="76"/>
-      <c r="Z86" s="76"/>
-      <c r="AA86" s="76" t="n">
+      <c r="T86" s="77"/>
+      <c r="U86" s="77"/>
+      <c r="V86" s="77"/>
+      <c r="W86" s="77"/>
+      <c r="X86" s="77"/>
+      <c r="Y86" s="77"/>
+      <c r="Z86" s="77"/>
+      <c r="AA86" s="77" t="n">
         <f aca="false">+(AA52-Z52)/(AA105-Z105)</f>
         <v>-1.03384279475983</v>
       </c>
-      <c r="AB86" s="76" t="n">
+      <c r="AB86" s="77" t="n">
         <f aca="false">+(AB52-AA52)/(AB105-AA105)</f>
         <v>2.94704684317719</v>
       </c>
-      <c r="AC86" s="76" t="n">
+      <c r="AC86" s="77" t="n">
         <f aca="false">+(AC52-AB52)/(AC105-AB105)</f>
         <v>1.32718894009217</v>
       </c>
-      <c r="AD86" s="76" t="n">
+      <c r="AD86" s="77" t="n">
         <f aca="false">+(AD52-AC52)/(AD105-AC105)</f>
         <v>0.434883720930233</v>
       </c>
-      <c r="AE86" s="76" t="n">
+      <c r="AE86" s="77" t="n">
         <f aca="false">+(AE52-AD52)/(AE105-AD105)</f>
         <v>2.2482782369146</v>
       </c>
-      <c r="AF86" s="76" t="n">
+      <c r="AF86" s="77" t="n">
         <f aca="false">+(AF52-AE52)/(AF105-AE105)</f>
         <v>1.11442495126706</v>
       </c>
-      <c r="AG86" s="76" t="n">
+      <c r="AG86" s="77" t="n">
         <f aca="false">+(AG52-AF52)/(AG105-AF105)</f>
         <v>0.563583287721219</v>
       </c>
-      <c r="AH86" s="76" t="n">
+      <c r="AH86" s="77" t="n">
         <f aca="false">+(AH52-AG52)/(AH105-AG105)</f>
         <v>-0.340883458646617</v>
       </c>
-      <c r="AI86" s="76" t="n">
+      <c r="AI86" s="77" t="n">
         <f aca="false">+(AI52-AH52)/(AI105-AH105)</f>
         <v>1.03404461687682</v>
       </c>
-      <c r="AJ86" s="76" t="n">
+      <c r="AJ86" s="77" t="n">
         <f aca="false">+(AJ52-AI52)/(AJ105-AI105)</f>
         <v>0.839684625492773</v>
       </c>
-      <c r="AK86" s="76" t="n">
+      <c r="AK86" s="77" t="n">
         <f aca="false">+(AK52-AJ52)/(AK105-AJ105)</f>
         <v>-0.744852365378415</v>
       </c>
-      <c r="AL86" s="76" t="n">
+      <c r="AL86" s="77" t="n">
         <f aca="false">+(AL52-AK52)/(AL105-AK105)</f>
         <v>0.931396098189701</v>
       </c>
-      <c r="AM86" s="76" t="n">
+      <c r="AM86" s="77" t="n">
         <f aca="false">+(AM52-AL52)/(AM105-AL105)</f>
         <v>0.939537138010421</v>
       </c>
-      <c r="AN86" s="76" t="n">
+      <c r="AN86" s="77" t="n">
         <f aca="false">+(AN52-AM52)/(AN105-AM105)</f>
         <v>-0.0345478984269989</v>
       </c>
-      <c r="AO86" s="76"/>
-      <c r="AP86" s="76"/>
-      <c r="AQ86" s="76"/>
-      <c r="AR86" s="77"/>
-      <c r="AS86" s="76"/>
-      <c r="AT86" s="76"/>
-      <c r="AU86" s="76"/>
-      <c r="AV86" s="76"/>
-      <c r="AW86" s="76"/>
-      <c r="AX86" s="76"/>
-      <c r="AY86" s="76"/>
-      <c r="AZ86" s="76"/>
-      <c r="BA86" s="76"/>
-      <c r="BB86" s="76"/>
-      <c r="BC86" s="76"/>
-      <c r="BD86" s="76"/>
-      <c r="BE86" s="76"/>
-      <c r="BF86" s="76"/>
-      <c r="BG86" s="76"/>
-      <c r="BH86" s="76"/>
-      <c r="BI86" s="76"/>
-      <c r="BJ86" s="76"/>
-      <c r="BK86" s="76"/>
-      <c r="BL86" s="76"/>
-      <c r="BM86" s="76"/>
-      <c r="BN86" s="76"/>
-      <c r="BO86" s="76"/>
-      <c r="BP86" s="76"/>
-      <c r="BQ86" s="76"/>
-      <c r="BR86" s="76"/>
-      <c r="BS86" s="76"/>
-      <c r="BT86" s="76"/>
-      <c r="BU86" s="76"/>
-      <c r="BV86" s="76"/>
-      <c r="BW86" s="76"/>
-      <c r="BX86" s="76"/>
-      <c r="BY86" s="76"/>
-      <c r="BZ86" s="76"/>
-      <c r="CA86" s="76"/>
-      <c r="CB86" s="76"/>
-      <c r="CC86" s="76"/>
-      <c r="CD86" s="76"/>
-      <c r="CE86" s="76"/>
-      <c r="CF86" s="76"/>
-      <c r="CG86" s="76"/>
-      <c r="CH86" s="76"/>
-      <c r="CI86" s="76"/>
-      <c r="CJ86" s="76"/>
-      <c r="CK86" s="76"/>
-      <c r="CL86" s="76"/>
-      <c r="CM86" s="76"/>
-      <c r="CN86" s="76"/>
-      <c r="CO86" s="76"/>
-      <c r="CP86" s="76"/>
-      <c r="CQ86" s="76"/>
-      <c r="CR86" s="76"/>
-      <c r="CS86" s="76"/>
-      <c r="CT86" s="76"/>
-      <c r="CU86" s="76"/>
-      <c r="CV86" s="76"/>
-      <c r="CW86" s="76"/>
-      <c r="CX86" s="76"/>
-      <c r="CY86" s="76"/>
-      <c r="CZ86" s="76"/>
-      <c r="DA86" s="76"/>
-      <c r="DB86" s="76"/>
-      <c r="DC86" s="76"/>
-      <c r="DD86" s="76"/>
-      <c r="DE86" s="76"/>
-      <c r="DF86" s="76"/>
-      <c r="DG86" s="76"/>
-      <c r="DH86" s="76"/>
-      <c r="DI86" s="76"/>
-      <c r="DJ86" s="76"/>
-      <c r="DK86" s="76"/>
-      <c r="DL86" s="76"/>
-      <c r="DM86" s="76"/>
-      <c r="DN86" s="76"/>
-      <c r="DO86" s="76"/>
-      <c r="DP86" s="76"/>
-      <c r="DQ86" s="76"/>
-      <c r="DR86" s="76"/>
-      <c r="DS86" s="76"/>
-      <c r="DT86" s="76"/>
-      <c r="DU86" s="76"/>
-      <c r="DV86" s="76"/>
-      <c r="DW86" s="76"/>
-      <c r="DX86" s="76"/>
-      <c r="DY86" s="76"/>
-      <c r="DZ86" s="76"/>
-      <c r="EA86" s="76"/>
-      <c r="EB86" s="76"/>
-      <c r="EC86" s="76"/>
-      <c r="ED86" s="76"/>
-      <c r="EE86" s="76"/>
-      <c r="EF86" s="76"/>
-      <c r="EG86" s="76"/>
-      <c r="EH86" s="76"/>
-      <c r="EI86" s="76"/>
-      <c r="EJ86" s="76"/>
-      <c r="EK86" s="76"/>
-      <c r="EL86" s="76"/>
-      <c r="EM86" s="76"/>
-      <c r="EN86" s="76"/>
-      <c r="EO86" s="76"/>
-      <c r="EP86" s="76"/>
-      <c r="EQ86" s="76"/>
-      <c r="ER86" s="76"/>
+      <c r="AO86" s="77"/>
+      <c r="AP86" s="77"/>
+      <c r="AQ86" s="77"/>
+      <c r="AR86" s="78"/>
+      <c r="AS86" s="77"/>
+      <c r="AT86" s="77"/>
+      <c r="AU86" s="77"/>
+      <c r="AV86" s="77"/>
+      <c r="AW86" s="77"/>
+      <c r="AX86" s="77"/>
+      <c r="AY86" s="77"/>
+      <c r="AZ86" s="77"/>
+      <c r="BA86" s="77"/>
+      <c r="BB86" s="77"/>
+      <c r="BC86" s="77"/>
+      <c r="BD86" s="77"/>
+      <c r="BE86" s="77"/>
+      <c r="BF86" s="77"/>
+      <c r="BG86" s="77"/>
+      <c r="BH86" s="77"/>
+      <c r="BI86" s="77"/>
+      <c r="BJ86" s="77"/>
+      <c r="BK86" s="77"/>
+      <c r="BL86" s="77"/>
+      <c r="BM86" s="77"/>
+      <c r="BN86" s="77"/>
+      <c r="BO86" s="77"/>
+      <c r="BP86" s="77"/>
+      <c r="BQ86" s="77"/>
+      <c r="BR86" s="77"/>
+      <c r="BS86" s="77"/>
+      <c r="BT86" s="77"/>
+      <c r="BU86" s="77"/>
+      <c r="BV86" s="77"/>
+      <c r="BW86" s="77"/>
+      <c r="BX86" s="77"/>
+      <c r="BY86" s="77"/>
+      <c r="BZ86" s="77"/>
+      <c r="CA86" s="77"/>
+      <c r="CB86" s="77"/>
+      <c r="CC86" s="77"/>
+      <c r="CD86" s="77"/>
+      <c r="CE86" s="77"/>
+      <c r="CF86" s="77"/>
+      <c r="CG86" s="77"/>
+      <c r="CH86" s="77"/>
+      <c r="CI86" s="77"/>
+      <c r="CJ86" s="77"/>
+      <c r="CK86" s="77"/>
+      <c r="CL86" s="77"/>
+      <c r="CM86" s="77"/>
+      <c r="CN86" s="77"/>
+      <c r="CO86" s="77"/>
+      <c r="CP86" s="77"/>
+      <c r="CQ86" s="77"/>
+      <c r="CR86" s="77"/>
+      <c r="CS86" s="77"/>
+      <c r="CT86" s="77"/>
+      <c r="CU86" s="77"/>
+      <c r="CV86" s="77"/>
+      <c r="CW86" s="77"/>
+      <c r="CX86" s="77"/>
+      <c r="CY86" s="77"/>
+      <c r="CZ86" s="77"/>
+      <c r="DA86" s="77"/>
+      <c r="DB86" s="77"/>
+      <c r="DC86" s="77"/>
+      <c r="DD86" s="77"/>
+      <c r="DE86" s="77"/>
+      <c r="DF86" s="77"/>
+      <c r="DG86" s="77"/>
+      <c r="DH86" s="77"/>
+      <c r="DI86" s="77"/>
+      <c r="DJ86" s="77"/>
+      <c r="DK86" s="77"/>
+      <c r="DL86" s="77"/>
+      <c r="DM86" s="77"/>
+      <c r="DN86" s="77"/>
+      <c r="DO86" s="77"/>
+      <c r="DP86" s="77"/>
+      <c r="DQ86" s="77"/>
+      <c r="DR86" s="77"/>
+      <c r="DS86" s="77"/>
+      <c r="DT86" s="77"/>
+      <c r="DU86" s="77"/>
+      <c r="DV86" s="77"/>
+      <c r="DW86" s="77"/>
+      <c r="DX86" s="77"/>
+      <c r="DY86" s="77"/>
+      <c r="DZ86" s="77"/>
+      <c r="EA86" s="77"/>
+      <c r="EB86" s="77"/>
+      <c r="EC86" s="77"/>
+      <c r="ED86" s="77"/>
+      <c r="EE86" s="77"/>
+      <c r="EF86" s="77"/>
+      <c r="EG86" s="77"/>
+      <c r="EH86" s="77"/>
+      <c r="EI86" s="77"/>
+      <c r="EJ86" s="77"/>
+      <c r="EK86" s="77"/>
+      <c r="EL86" s="77"/>
+      <c r="EM86" s="77"/>
+      <c r="EN86" s="77"/>
+      <c r="EO86" s="77"/>
+      <c r="EP86" s="77"/>
+      <c r="EQ86" s="77"/>
+      <c r="ER86" s="77"/>
     </row>
     <row r="87" s="35" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="58"/>
@@ -25537,39 +29798,39 @@
       </c>
       <c r="AQ91" s="39" t="n">
         <f aca="false">+AP91+AQ52</f>
-        <v>375923.406649559</v>
+        <v>360836.487097559</v>
       </c>
       <c r="AR91" s="39" t="n">
         <f aca="false">+AQ91+AR52</f>
-        <v>517160.302935549</v>
+        <v>487698.211448061</v>
       </c>
       <c r="AS91" s="39" t="n">
         <f aca="false">+AR91+AS52</f>
-        <v>690855.34706245</v>
+        <v>635372.355542475</v>
       </c>
       <c r="AT91" s="39" t="n">
         <f aca="false">+AS91+AT52</f>
-        <v>904882.599319588</v>
+        <v>816356.223171239</v>
       </c>
       <c r="AU91" s="39" t="n">
         <f aca="false">+AT91+AU52</f>
-        <v>1146428.86639612</v>
+        <v>1024539.90544681</v>
       </c>
       <c r="AV91" s="39" t="n">
         <f aca="false">+AU91+AV52</f>
-        <v>1432313.8810187</v>
+        <v>1263745.97286726</v>
       </c>
       <c r="AW91" s="39" t="n">
         <f aca="false">+AV91+AW52</f>
-        <v>1754581.48710516</v>
+        <v>1533284.4262809</v>
       </c>
       <c r="AX91" s="39" t="n">
         <f aca="false">+AW91+AX52</f>
-        <v>2117626.66508709</v>
+        <v>1836817.93921755</v>
       </c>
       <c r="AY91" s="39" t="n">
         <f aca="false">+AX91+AY52</f>
-        <v>2526372.20002026</v>
+        <v>2228995.52660115</v>
       </c>
       <c r="AZ91" s="39"/>
       <c r="BA91" s="39"/>
@@ -25965,46 +30226,46 @@
       </c>
       <c r="AQ93" s="3" t="n">
         <f aca="false">+AQ44*(1-AQ69)</f>
-        <v>144834.4276992</v>
+        <v>129747.5081472</v>
       </c>
       <c r="AR93" s="3" t="n">
         <f aca="false">+AR44*(1-AR69)</f>
-        <v>135973.968592896</v>
+        <v>121810.013531136</v>
       </c>
       <c r="AS93" s="3" t="n">
         <f aca="false">+AS44*(1-AS69)</f>
-        <v>166454.799885803</v>
+        <v>140846.369134141</v>
       </c>
       <c r="AT93" s="3" t="n">
         <f aca="false">+AT44*(1-AT69)</f>
-        <v>204355.277398263</v>
+        <v>172088.654651169</v>
       </c>
       <c r="AU93" s="3" t="n">
         <f aca="false">+AU44*(1-AU69)</f>
-        <v>228877.910686055</v>
+        <v>196754.69515117</v>
       </c>
       <c r="AV93" s="3" t="n">
         <f aca="false">+AV44*(1-AV69)</f>
-        <v>269835.010493034</v>
+        <v>224862.508744195</v>
       </c>
       <c r="AW93" s="3" t="n">
         <f aca="false">+AW44*(1-AW69)</f>
-        <v>302215.211752198</v>
+        <v>251846.009793498</v>
       </c>
       <c r="AX93" s="3" t="n">
         <f aca="false">+AX44*(1-AX69)</f>
-        <v>338481.037162461</v>
+        <v>282067.530968718</v>
       </c>
       <c r="AY93" s="3" t="n">
         <f aca="false">+AY44*(1-AY69)</f>
-        <v>379098.761621957</v>
+        <v>366462.136234558</v>
       </c>
       <c r="AZ93" s="39"/>
-      <c r="BA93" s="78" t="s">
+      <c r="BA93" s="79" t="s">
         <v>180</v>
       </c>
-      <c r="BB93" s="79" t="n">
-        <v>0.01</v>
+      <c r="BB93" s="80" t="n">
+        <v>0.02</v>
       </c>
       <c r="BC93" s="39"/>
       <c r="BD93" s="39"/>
@@ -26287,7 +30548,7 @@
       </c>
       <c r="BB94" s="66" t="n">
         <f aca="false">+Main!E12</f>
-        <v>0.112193487547429</v>
+        <v>0.108897277026286</v>
       </c>
       <c r="BC94" s="39"/>
       <c r="BD94" s="39"/>
@@ -26518,51 +30779,51 @@
       </c>
       <c r="AP95" s="3" t="n">
         <f aca="false">+AP93+AP129-AP144-(AP94-AO94)</f>
-        <v>-40798.4707530917</v>
+        <v>-40798.4707530918</v>
       </c>
       <c r="AQ95" s="3" t="n">
         <f aca="false">+AQ93+AQ129-AQ144-(AQ94-AP94)</f>
-        <v>109398.18958302</v>
+        <v>94311.2700310196</v>
       </c>
       <c r="AR95" s="3" t="n">
         <f aca="false">+AR93+AR129-AR144-(AR94-AQ94)</f>
-        <v>97349.2402319708</v>
+        <v>83185.2851702108</v>
       </c>
       <c r="AS95" s="3" t="n">
         <f aca="false">+AS93+AS129-AS144-(AS94-AR94)</f>
-        <v>143501.20074283</v>
+        <v>117892.769991168</v>
       </c>
       <c r="AT95" s="3" t="n">
         <f aca="false">+AT93+AT129-AT144-(AT94-AS94)</f>
-        <v>181682.079177225</v>
+        <v>149415.456430131</v>
       </c>
       <c r="AU95" s="3" t="n">
         <f aca="false">+AU93+AU129-AU144-(AU94-AT94)</f>
-        <v>203426.408114561</v>
+        <v>171303.192579676</v>
       </c>
       <c r="AV95" s="3" t="n">
         <f aca="false">+AV93+AV129-AV144-(AV94-AU94)</f>
-        <v>242881.40807163</v>
+        <v>197908.906322791</v>
       </c>
       <c r="AW95" s="3" t="n">
         <f aca="false">+AW93+AW129-AW144-(AW94-AV94)</f>
-        <v>273757.579289839</v>
+        <v>223388.37733114</v>
       </c>
       <c r="AX95" s="3" t="n">
         <f aca="false">+AX93+AX129-AX144-(AX94-AW94)</f>
-        <v>310852.087677628</v>
+        <v>254438.581483884</v>
       </c>
       <c r="AY95" s="3" t="n">
         <f aca="false">+AY93+AY129-AY144-(AY94-AX94)</f>
-        <v>348285.22300644</v>
+        <v>335648.597619043</v>
       </c>
       <c r="AZ95" s="39"/>
       <c r="BA95" s="63" t="s">
         <v>14</v>
       </c>
-      <c r="BB95" s="68" t="n">
+      <c r="BB95" s="69" t="n">
         <f aca="false">+NPV(BB94,AO95:AX95,AY95+BB96)</f>
-        <v>1877014.09025624</v>
+        <v>1929829.38170495</v>
       </c>
       <c r="BC95" s="39"/>
       <c r="BD95" s="39"/>
@@ -26659,160 +30920,160 @@
       <c r="EQ95" s="39"/>
       <c r="ER95" s="39"/>
     </row>
-    <row r="96" s="80" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="77" t="s">
+    <row r="96" s="81" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A96" s="78" t="s">
         <v>186</v>
       </c>
-      <c r="B96" s="77"/>
-      <c r="C96" s="77" t="n">
+      <c r="B96" s="78"/>
+      <c r="C96" s="78" t="n">
         <f aca="false">+(C93*4)/(AVERAGE(B116:C116)+AVERAGE(B124:C124))</f>
         <v>0.219361956246618</v>
       </c>
-      <c r="D96" s="77" t="n">
+      <c r="D96" s="78" t="n">
         <f aca="false">+(D93*4)/(AVERAGE(C116:D116)+AVERAGE(C124:D124))</f>
         <v>0.137479713437688</v>
       </c>
-      <c r="E96" s="77" t="n">
+      <c r="E96" s="78" t="n">
         <f aca="false">+(E93*4)/(AVERAGE(D116:E116)+AVERAGE(D124:E124))</f>
         <v>0.143626198061217</v>
       </c>
-      <c r="F96" s="77" t="n">
+      <c r="F96" s="78" t="n">
         <f aca="false">+(F93*4)/(AVERAGE(E116:F116)+AVERAGE(E124:F124))</f>
         <v>0.167083269532327</v>
       </c>
-      <c r="G96" s="77" t="n">
+      <c r="G96" s="78" t="n">
         <f aca="false">+(G93*4)/(AVERAGE(F116:G116)+AVERAGE(F124:G124))</f>
         <v>0.219296622547075</v>
       </c>
-      <c r="H96" s="77" t="n">
+      <c r="H96" s="78" t="n">
         <f aca="false">+(H93*4)/(AVERAGE(G116:H116)+AVERAGE(G124:H124))</f>
         <v>0.289686452005504</v>
       </c>
-      <c r="I96" s="77" t="n">
+      <c r="I96" s="78" t="n">
         <f aca="false">+(I93*4)/(AVERAGE(H116:I116)+AVERAGE(H124:I124))</f>
         <v>0.328438377499268</v>
       </c>
-      <c r="J96" s="77" t="n">
+      <c r="J96" s="78" t="n">
         <f aca="false">+(J93*4)/(AVERAGE(I116:J116)+AVERAGE(I124:J124))</f>
         <v>0.28398901468612</v>
       </c>
-      <c r="K96" s="77" t="n">
+      <c r="K96" s="78" t="n">
         <f aca="false">+(K93*4)/(AVERAGE(J116:K116)+AVERAGE(J124:K124))</f>
         <v>0.308606708264593</v>
       </c>
-      <c r="L96" s="77" t="n">
+      <c r="L96" s="78" t="n">
         <f aca="false">+(L93*4)/(AVERAGE(K116:L116)+AVERAGE(K124:L124))</f>
         <v>0.331557152458149</v>
       </c>
-      <c r="M96" s="77" t="n">
+      <c r="M96" s="78" t="n">
         <f aca="false">+(M93*4)/(AVERAGE(L116:M116)+AVERAGE(L124:M124))</f>
         <v>0.408515912200832</v>
       </c>
-      <c r="N96" s="77" t="n">
+      <c r="N96" s="78" t="n">
         <f aca="false">+(N93*4)/(AVERAGE(M116:N116)+AVERAGE(M124:N124))</f>
         <v>0.298977798616802</v>
       </c>
-      <c r="O96" s="77" t="n">
+      <c r="O96" s="78" t="n">
         <f aca="false">+(O93*4)/(AVERAGE(N116:O116)+AVERAGE(N124:O124))</f>
         <v>0.334244931395724</v>
       </c>
-      <c r="P96" s="77" t="n">
+      <c r="P96" s="78" t="n">
         <f aca="false">+(P93*4)/(AVERAGE(O116:P116)+AVERAGE(O124:P124))</f>
         <v>0.31398978667852</v>
       </c>
-      <c r="Q96" s="77" t="n">
+      <c r="Q96" s="78" t="n">
         <f aca="false">+(Q93*4)/(AVERAGE(P116:Q116)+AVERAGE(P124:Q124))</f>
         <v>0.356331039387326</v>
       </c>
-      <c r="R96" s="77" t="n">
+      <c r="R96" s="78" t="n">
         <f aca="false">+(R93*4)/(AVERAGE(Q116:R116)+AVERAGE(Q124:R124))</f>
         <v>0.385918477554553</v>
       </c>
-      <c r="S96" s="77" t="n">
+      <c r="S96" s="78" t="n">
         <f aca="false">+(S93*4)/(AVERAGE(R116:S116)+AVERAGE(R124:S124))</f>
         <v>0.196060078037336</v>
       </c>
-      <c r="T96" s="77"/>
-      <c r="U96" s="77"/>
-      <c r="V96" s="77"/>
-      <c r="W96" s="77"/>
-      <c r="X96" s="77"/>
-      <c r="Y96" s="77"/>
-      <c r="Z96" s="77"/>
-      <c r="AA96" s="77" t="n">
+      <c r="T96" s="78"/>
+      <c r="U96" s="78"/>
+      <c r="V96" s="78"/>
+      <c r="W96" s="78"/>
+      <c r="X96" s="78"/>
+      <c r="Y96" s="78"/>
+      <c r="Z96" s="78"/>
+      <c r="AA96" s="78" t="n">
         <f aca="false">+AA93/(AVERAGE(Z116:AA116)+AVERAGE(Z124:AA124))</f>
         <v>0.0063590005258653</v>
       </c>
-      <c r="AB96" s="77" t="n">
+      <c r="AB96" s="78" t="n">
         <f aca="false">+AB93/(AVERAGE(AA116:AB116)+AVERAGE(AA124:AB124))</f>
         <v>0.106334768701021</v>
       </c>
-      <c r="AC96" s="77" t="n">
+      <c r="AC96" s="78" t="n">
         <f aca="false">+AC93/(AVERAGE(AB116:AC116)+AVERAGE(AB124:AC124))</f>
         <v>0.115979418700002</v>
       </c>
-      <c r="AD96" s="77" t="n">
+      <c r="AD96" s="78" t="n">
         <f aca="false">+AD93/(AVERAGE(AC116:AD116)+AVERAGE(AC124:AD124))</f>
         <v>0.092299172309872</v>
       </c>
-      <c r="AE96" s="77" t="n">
+      <c r="AE96" s="78" t="n">
         <f aca="false">+AE93/(AVERAGE(AD116:AE116)+AVERAGE(AD124:AE124))</f>
         <v>0.196161513032188</v>
       </c>
-      <c r="AF96" s="77" t="n">
+      <c r="AF96" s="78" t="n">
         <f aca="false">+AF93/(AVERAGE(AE116:AF116)+AVERAGE(AE124:AF124))</f>
         <v>0.234107506819079</v>
       </c>
-      <c r="AG96" s="77" t="n">
+      <c r="AG96" s="78" t="n">
         <f aca="false">+AG93/(AVERAGE(AF116:AG116)+AVERAGE(AF124:AG124))</f>
         <v>0.274131949978579</v>
       </c>
-      <c r="AH96" s="77" t="n">
+      <c r="AH96" s="78" t="n">
         <f aca="false">+AH93/(AVERAGE(AG116:AH116)+AVERAGE(AG124:AH124))</f>
         <v>0.192996344145235</v>
       </c>
-      <c r="AI96" s="77" t="n">
+      <c r="AI96" s="78" t="n">
         <f aca="false">+AI93/(AVERAGE(AH116:AI116)+AVERAGE(AH124:AI124))</f>
         <v>0.25026932333691</v>
       </c>
-      <c r="AJ96" s="77" t="n">
+      <c r="AJ96" s="78" t="n">
         <f aca="false">+AJ93/(AVERAGE(AI116:AJ116)+AVERAGE(AI124:AJ124))</f>
         <v>0.307524810176702</v>
       </c>
-      <c r="AK96" s="77" t="n">
+      <c r="AK96" s="78" t="n">
         <f aca="false">+AK93/(AVERAGE(AJ116:AK116)+AVERAGE(AJ124:AK124))</f>
         <v>0.178881277913966</v>
       </c>
-      <c r="AL96" s="77" t="n">
+      <c r="AL96" s="78" t="n">
         <f aca="false">+AL93/(AVERAGE(AK116:AL116)+AVERAGE(AK124:AL124))</f>
         <v>0.250919822360031</v>
       </c>
-      <c r="AM96" s="77" t="n">
+      <c r="AM96" s="78" t="n">
         <f aca="false">+AM93/(AVERAGE(AL116:AM116)+AVERAGE(AL124:AM124))</f>
         <v>0.319713820155131</v>
       </c>
-      <c r="AN96" s="77" t="n">
+      <c r="AN96" s="78" t="n">
         <f aca="false">+AN93/(AVERAGE(AM116:AN116)+AVERAGE(AM124:AN124))</f>
         <v>0.240391237937521</v>
       </c>
-      <c r="AO96" s="77"/>
-      <c r="AP96" s="77"/>
-      <c r="AQ96" s="77"/>
-      <c r="AR96" s="77"/>
-      <c r="AS96" s="77"/>
-      <c r="AT96" s="77"/>
-      <c r="AU96" s="77"/>
-      <c r="AV96" s="77"/>
-      <c r="AW96" s="77"/>
-      <c r="AX96" s="77"/>
-      <c r="AY96" s="77"/>
+      <c r="AO96" s="78"/>
+      <c r="AP96" s="78"/>
+      <c r="AQ96" s="78"/>
+      <c r="AR96" s="78"/>
+      <c r="AS96" s="78"/>
+      <c r="AT96" s="78"/>
+      <c r="AU96" s="78"/>
+      <c r="AV96" s="78"/>
+      <c r="AW96" s="78"/>
+      <c r="AX96" s="78"/>
+      <c r="AY96" s="78"/>
       <c r="AZ96" s="39"/>
       <c r="BA96" s="65" t="s">
         <v>213</v>
       </c>
-      <c r="BB96" s="71" t="n">
+      <c r="BB96" s="72" t="n">
         <f aca="false">+AY95*(1+BB93)/(BB94-BB93)</f>
-        <v>3442177.02789766</v>
+        <v>3851204.23283823</v>
       </c>
       <c r="BC96" s="39"/>
       <c r="BD96" s="39"/>
@@ -26962,12 +31223,12 @@
       <c r="AX97" s="3"/>
       <c r="AY97" s="3"/>
       <c r="AZ97" s="39"/>
-      <c r="BA97" s="72" t="s">
-        <v>193</v>
-      </c>
-      <c r="BB97" s="73" t="n">
+      <c r="BA97" s="73" t="s">
+        <v>188</v>
+      </c>
+      <c r="BB97" s="74" t="n">
         <f aca="false">+BB95/Main!F7-1</f>
-        <v>0.254325787211558</v>
+        <v>0.289619918655277</v>
       </c>
       <c r="BC97" s="39"/>
       <c r="BD97" s="39"/>
@@ -27066,8 +31327,8 @@
     </row>
     <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AZ98" s="62"/>
-      <c r="BA98" s="80"/>
-      <c r="BB98" s="80"/>
+      <c r="BA98" s="81"/>
+      <c r="BB98" s="81"/>
       <c r="BC98" s="62"/>
       <c r="BD98" s="62"/>
       <c r="BE98" s="62"/>
@@ -27624,47 +31885,47 @@
       <c r="AN102" s="3" t="n">
         <v>7361</v>
       </c>
-      <c r="AO102" s="81" t="n">
+      <c r="AO102" s="82" t="n">
         <f aca="false">+AO30*0.035</f>
         <v>9003.2768</v>
       </c>
-      <c r="AP102" s="81" t="n">
+      <c r="AP102" s="82" t="n">
         <f aca="false">+AP30*0.035</f>
         <v>10803.93216</v>
       </c>
-      <c r="AQ102" s="81" t="n">
+      <c r="AQ102" s="82" t="n">
         <f aca="false">+AQ30*0.035</f>
         <v>12424.521984</v>
       </c>
-      <c r="AR102" s="81" t="n">
+      <c r="AR102" s="82" t="n">
         <f aca="false">+AR30*0.035</f>
         <v>14163.95506176</v>
       </c>
-      <c r="AS102" s="81" t="n">
+      <c r="AS102" s="82" t="n">
         <f aca="false">+AS30*0.035</f>
         <v>16005.2692197888</v>
       </c>
-      <c r="AT102" s="81" t="n">
+      <c r="AT102" s="82" t="n">
         <f aca="false">+AT30*0.035</f>
         <v>17925.9015261635</v>
       </c>
-      <c r="AU102" s="81" t="n">
+      <c r="AU102" s="82" t="n">
         <f aca="false">+AU30*0.035</f>
         <v>20077.0097093031</v>
       </c>
-      <c r="AV102" s="81" t="n">
+      <c r="AV102" s="82" t="n">
         <f aca="false">+AV30*0.035</f>
         <v>22486.2508744194</v>
       </c>
-      <c r="AW102" s="81" t="n">
+      <c r="AW102" s="82" t="n">
         <f aca="false">+AW30*0.035</f>
         <v>25184.6009793498</v>
       </c>
-      <c r="AX102" s="81" t="n">
+      <c r="AX102" s="82" t="n">
         <f aca="false">+AX30*0.035</f>
         <v>28206.7530968718</v>
       </c>
-      <c r="AY102" s="81" t="n">
+      <c r="AY102" s="82" t="n">
         <f aca="false">+AY30*0.035</f>
         <v>31591.5634684964</v>
       </c>
@@ -28796,47 +33057,47 @@
         <f aca="false">+22940+2213</f>
         <v>25153</v>
       </c>
-      <c r="AO112" s="81" t="n">
+      <c r="AO112" s="82" t="n">
         <f aca="false">+AO30*0.12</f>
         <v>30868.3776</v>
       </c>
-      <c r="AP112" s="81" t="n">
+      <c r="AP112" s="82" t="n">
         <f aca="false">+AP30*0.12</f>
         <v>37042.05312</v>
       </c>
-      <c r="AQ112" s="81" t="n">
+      <c r="AQ112" s="82" t="n">
         <f aca="false">+AQ30*0.12</f>
         <v>42598.361088</v>
       </c>
-      <c r="AR112" s="81" t="n">
+      <c r="AR112" s="82" t="n">
         <f aca="false">+AR30*0.12</f>
         <v>48562.13164032</v>
       </c>
-      <c r="AS112" s="81" t="n">
+      <c r="AS112" s="82" t="n">
         <f aca="false">+AS30*0.12</f>
         <v>54875.2087535616</v>
       </c>
-      <c r="AT112" s="81" t="n">
+      <c r="AT112" s="82" t="n">
         <f aca="false">+AT30*0.12</f>
         <v>61460.233803989</v>
       </c>
-      <c r="AU112" s="81" t="n">
+      <c r="AU112" s="82" t="n">
         <f aca="false">+AU30*0.12</f>
         <v>68835.4618604677</v>
       </c>
-      <c r="AV112" s="81" t="n">
+      <c r="AV112" s="82" t="n">
         <f aca="false">+AV30*0.12</f>
         <v>77095.7172837238</v>
       </c>
-      <c r="AW112" s="81" t="n">
+      <c r="AW112" s="82" t="n">
         <f aca="false">+AW30*0.12</f>
         <v>86347.2033577707</v>
       </c>
-      <c r="AX112" s="81" t="n">
+      <c r="AX112" s="82" t="n">
         <f aca="false">+AX30*0.12</f>
         <v>96708.8677607032</v>
       </c>
-      <c r="AY112" s="81" t="n">
+      <c r="AY112" s="82" t="n">
         <f aca="false">+AY30*0.12</f>
         <v>108313.931891988</v>
       </c>
@@ -29122,47 +33383,47 @@
       <c r="AN114" s="3" t="n">
         <v>30729</v>
       </c>
-      <c r="AO114" s="81" t="n">
+      <c r="AO114" s="82" t="n">
         <f aca="false">+AO30*0.13</f>
         <v>33440.7424</v>
       </c>
-      <c r="AP114" s="81" t="n">
+      <c r="AP114" s="82" t="n">
         <f aca="false">+AP30*0.13</f>
         <v>40128.89088</v>
       </c>
-      <c r="AQ114" s="81" t="n">
+      <c r="AQ114" s="82" t="n">
         <f aca="false">+AQ30*0.13</f>
         <v>46148.224512</v>
       </c>
-      <c r="AR114" s="81" t="n">
+      <c r="AR114" s="82" t="n">
         <f aca="false">+AR30*0.13</f>
         <v>52608.97594368</v>
       </c>
-      <c r="AS114" s="81" t="n">
+      <c r="AS114" s="82" t="n">
         <f aca="false">+AS30*0.13</f>
         <v>59448.1428163584</v>
       </c>
-      <c r="AT114" s="81" t="n">
+      <c r="AT114" s="82" t="n">
         <f aca="false">+AT30*0.13</f>
         <v>66581.9199543215</v>
       </c>
-      <c r="AU114" s="81" t="n">
+      <c r="AU114" s="82" t="n">
         <f aca="false">+AU30*0.13</f>
         <v>74571.75034884</v>
       </c>
-      <c r="AV114" s="81" t="n">
+      <c r="AV114" s="82" t="n">
         <f aca="false">+AV30*0.13</f>
         <v>83520.3603907008</v>
       </c>
-      <c r="AW114" s="81" t="n">
+      <c r="AW114" s="82" t="n">
         <f aca="false">+AW30*0.13</f>
         <v>93542.8036375849</v>
       </c>
-      <c r="AX114" s="81" t="n">
+      <c r="AX114" s="82" t="n">
         <f aca="false">+AX30*0.13</f>
         <v>104767.940074095</v>
       </c>
-      <c r="AY114" s="81" t="n">
+      <c r="AY114" s="82" t="n">
         <f aca="false">+AY30*0.13</f>
         <v>117340.092882986</v>
       </c>
@@ -30366,7 +34627,7 @@
         <v>217243</v>
       </c>
     </row>
-    <row r="125" s="82" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="125" s="83" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="3" t="s">
         <v>232</v>
       </c>
@@ -30913,42 +35174,42 @@
       </c>
       <c r="AQ127" s="3" t="n">
         <f aca="false">AQ52</f>
-        <v>148697.271988439</v>
+        <v>133610.352436439</v>
       </c>
       <c r="AR127" s="3" t="n">
         <f aca="false">AR52</f>
-        <v>141236.89628599</v>
+        <v>126861.724350502</v>
       </c>
       <c r="AS127" s="3" t="n">
         <f aca="false">AS52</f>
-        <v>173695.044126901</v>
+        <v>147674.144094414</v>
       </c>
       <c r="AT127" s="3" t="n">
         <f aca="false">AT52</f>
-        <v>214027.252257138</v>
+        <v>180983.867628764</v>
       </c>
       <c r="AU127" s="3" t="n">
         <f aca="false">AU52</f>
-        <v>241546.267076529</v>
+        <v>208183.682275568</v>
       </c>
       <c r="AV127" s="3" t="n">
         <f aca="false">AV52</f>
-        <v>285885.014622579</v>
+        <v>239206.06742045</v>
       </c>
       <c r="AW127" s="3" t="n">
         <f aca="false">AW52</f>
-        <v>322267.606086459</v>
+        <v>269538.45341364</v>
       </c>
       <c r="AX127" s="3" t="n">
         <f aca="false">AX52</f>
-        <v>363045.177981933</v>
+        <v>303533.51293665</v>
       </c>
       <c r="AY127" s="3" t="n">
         <f aca="false">AY52</f>
-        <v>408745.534933176</v>
-      </c>
-      <c r="BA127" s="82"/>
-      <c r="BB127" s="82"/>
+        <v>392177.587383604</v>
+      </c>
+      <c r="BA127" s="83"/>
+      <c r="BB127" s="83"/>
     </row>
     <row r="128" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="3" t="s">
@@ -31159,47 +35420,47 @@
       <c r="AN129" s="3" t="n">
         <v>18616</v>
       </c>
-      <c r="AO129" s="81" t="n">
+      <c r="AO129" s="82" t="n">
         <f aca="false">+AN129*1.15</f>
         <v>21408.4</v>
       </c>
-      <c r="AP129" s="81" t="n">
+      <c r="AP129" s="82" t="n">
         <f aca="false">+AO129*1.15</f>
         <v>24619.66</v>
       </c>
-      <c r="AQ129" s="81" t="n">
+      <c r="AQ129" s="82" t="n">
         <f aca="false">+AP129*1.15</f>
         <v>28312.609</v>
       </c>
-      <c r="AR129" s="81" t="n">
+      <c r="AR129" s="82" t="n">
         <f aca="false">+AQ129*1.15</f>
         <v>32559.50035</v>
       </c>
-      <c r="AS129" s="81" t="n">
+      <c r="AS129" s="82" t="n">
         <f aca="false">+AR129*1.15</f>
         <v>37443.4254025</v>
       </c>
-      <c r="AT129" s="81" t="n">
+      <c r="AT129" s="82" t="n">
         <f aca="false">+AS129*1.15</f>
         <v>43059.939212875</v>
       </c>
-      <c r="AU129" s="81" t="n">
+      <c r="AU129" s="82" t="n">
         <f aca="false">+AT129*1.15</f>
         <v>49518.9300948062</v>
       </c>
-      <c r="AV129" s="81" t="n">
+      <c r="AV129" s="82" t="n">
         <f aca="false">+AU129*1.15</f>
         <v>56946.7696090272</v>
       </c>
-      <c r="AW129" s="81" t="n">
+      <c r="AW129" s="82" t="n">
         <f aca="false">+AV129*1.15</f>
         <v>65488.7850503812</v>
       </c>
-      <c r="AX129" s="81" t="n">
+      <c r="AX129" s="82" t="n">
         <f aca="false">+AW129*1.15</f>
         <v>75312.1028079384</v>
       </c>
-      <c r="AY129" s="81" t="n">
+      <c r="AY129" s="82" t="n">
         <f aca="false">+AX129*1.15</f>
         <v>86608.9182291292</v>
       </c>
@@ -32541,7 +36802,7 @@
         <v>-14</v>
       </c>
     </row>
-    <row r="140" s="82" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="140" s="83" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="3" t="s">
         <v>224</v>
       </c>
@@ -33148,8 +37409,8 @@
       <c r="AX142" s="51"/>
       <c r="AY142" s="51"/>
       <c r="AZ142" s="3"/>
-      <c r="BA142" s="82"/>
-      <c r="BB142" s="82"/>
+      <c r="BA142" s="83"/>
+      <c r="BB142" s="83"/>
       <c r="BC142" s="3"/>
       <c r="BD142" s="3"/>
       <c r="BE142" s="3"/>
@@ -33249,7 +37510,7 @@
       <c r="BA143" s="35"/>
       <c r="BB143" s="35"/>
     </row>
-    <row r="144" s="82" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="144" s="83" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="3" t="s">
         <v>242</v>
       </c>
@@ -33358,46 +37619,46 @@
       <c r="AN144" s="3" t="n">
         <v>69691</v>
       </c>
-      <c r="AO144" s="81" t="n">
+      <c r="AO144" s="82" t="n">
         <v>167000</v>
       </c>
-      <c r="AP144" s="81" t="n">
+      <c r="AP144" s="82" t="n">
         <f aca="false">+AP30*0.6</f>
         <v>185210.2656</v>
       </c>
-      <c r="AQ144" s="81" t="n">
+      <c r="AQ144" s="82" t="n">
         <f aca="false">+AQ30*0.2</f>
         <v>70997.26848</v>
       </c>
-      <c r="AR144" s="81" t="n">
+      <c r="AR144" s="82" t="n">
         <f aca="false">+AR30*0.2</f>
         <v>80936.8860672</v>
       </c>
-      <c r="AS144" s="81" t="n">
+      <c r="AS144" s="82" t="n">
         <f aca="false">+AS30*0.15</f>
         <v>68594.010941952</v>
       </c>
-      <c r="AT144" s="81" t="n">
+      <c r="AT144" s="82" t="n">
         <f aca="false">+AT30*0.15</f>
         <v>76825.2922549863</v>
       </c>
-      <c r="AU144" s="81" t="n">
+      <c r="AU144" s="82" t="n">
         <f aca="false">+AU30*0.15</f>
         <v>86044.3273255847</v>
       </c>
-      <c r="AV144" s="81" t="n">
+      <c r="AV144" s="82" t="n">
         <f aca="false">+AV30*0.15</f>
         <v>96369.6466046547</v>
       </c>
-      <c r="AW144" s="81" t="n">
+      <c r="AW144" s="82" t="n">
         <f aca="false">+AW30*0.15</f>
         <v>107934.004197213</v>
       </c>
-      <c r="AX144" s="81" t="n">
+      <c r="AX144" s="82" t="n">
         <f aca="false">+AX30*0.15</f>
         <v>120886.084700879</v>
       </c>
-      <c r="AY144" s="81" t="n">
+      <c r="AY144" s="82" t="n">
         <f aca="false">+AY30*0.15</f>
         <v>135392.414864984</v>
       </c>
@@ -33728,8 +37989,8 @@
       <c r="AX146" s="3"/>
       <c r="AY146" s="3"/>
       <c r="AZ146" s="3"/>
-      <c r="BA146" s="82"/>
-      <c r="BB146" s="82"/>
+      <c r="BA146" s="83"/>
+      <c r="BB146" s="83"/>
       <c r="BC146" s="3"/>
       <c r="BD146" s="3"/>
       <c r="BE146" s="3"/>
@@ -34441,154 +38702,154 @@
       <c r="ER149" s="35"/>
     </row>
     <row r="150" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A150" s="83"/>
-      <c r="B150" s="83"/>
-      <c r="C150" s="83"/>
-      <c r="D150" s="83"/>
-      <c r="E150" s="83"/>
-      <c r="F150" s="83"/>
-      <c r="G150" s="83"/>
-      <c r="H150" s="83"/>
-      <c r="I150" s="83"/>
-      <c r="J150" s="83"/>
-      <c r="K150" s="83"/>
-      <c r="L150" s="83"/>
-      <c r="M150" s="83"/>
-      <c r="N150" s="83"/>
-      <c r="O150" s="83"/>
-      <c r="P150" s="83"/>
-      <c r="Q150" s="83"/>
-      <c r="R150" s="83"/>
-      <c r="S150" s="83"/>
-      <c r="T150" s="83"/>
-      <c r="U150" s="83"/>
-      <c r="V150" s="83"/>
-      <c r="W150" s="83"/>
-      <c r="X150" s="83"/>
-      <c r="Y150" s="83"/>
-      <c r="Z150" s="83"/>
-      <c r="AA150" s="83"/>
-      <c r="AB150" s="83"/>
-      <c r="AC150" s="83"/>
-      <c r="AD150" s="83"/>
-      <c r="AE150" s="83"/>
-      <c r="AF150" s="83"/>
-      <c r="AG150" s="83"/>
-      <c r="AH150" s="83"/>
-      <c r="AI150" s="83"/>
-      <c r="AJ150" s="83"/>
-      <c r="AK150" s="83"/>
-      <c r="AL150" s="83"/>
-      <c r="AM150" s="83"/>
-      <c r="AN150" s="83"/>
-      <c r="AO150" s="83"/>
-      <c r="AP150" s="83"/>
-      <c r="AQ150" s="83"/>
-      <c r="AR150" s="84"/>
-      <c r="AS150" s="85"/>
-      <c r="AT150" s="85"/>
-      <c r="AU150" s="85"/>
-      <c r="AV150" s="85"/>
-      <c r="AW150" s="85"/>
-      <c r="AX150" s="85"/>
-      <c r="AY150" s="85"/>
-      <c r="AZ150" s="80"/>
+      <c r="A150" s="84"/>
+      <c r="B150" s="84"/>
+      <c r="C150" s="84"/>
+      <c r="D150" s="84"/>
+      <c r="E150" s="84"/>
+      <c r="F150" s="84"/>
+      <c r="G150" s="84"/>
+      <c r="H150" s="84"/>
+      <c r="I150" s="84"/>
+      <c r="J150" s="84"/>
+      <c r="K150" s="84"/>
+      <c r="L150" s="84"/>
+      <c r="M150" s="84"/>
+      <c r="N150" s="84"/>
+      <c r="O150" s="84"/>
+      <c r="P150" s="84"/>
+      <c r="Q150" s="84"/>
+      <c r="R150" s="84"/>
+      <c r="S150" s="84"/>
+      <c r="T150" s="84"/>
+      <c r="U150" s="84"/>
+      <c r="V150" s="84"/>
+      <c r="W150" s="84"/>
+      <c r="X150" s="84"/>
+      <c r="Y150" s="84"/>
+      <c r="Z150" s="84"/>
+      <c r="AA150" s="84"/>
+      <c r="AB150" s="84"/>
+      <c r="AC150" s="84"/>
+      <c r="AD150" s="84"/>
+      <c r="AE150" s="84"/>
+      <c r="AF150" s="84"/>
+      <c r="AG150" s="84"/>
+      <c r="AH150" s="84"/>
+      <c r="AI150" s="84"/>
+      <c r="AJ150" s="84"/>
+      <c r="AK150" s="84"/>
+      <c r="AL150" s="84"/>
+      <c r="AM150" s="84"/>
+      <c r="AN150" s="84"/>
+      <c r="AO150" s="84"/>
+      <c r="AP150" s="84"/>
+      <c r="AQ150" s="84"/>
+      <c r="AR150" s="85"/>
+      <c r="AS150" s="86"/>
+      <c r="AT150" s="86"/>
+      <c r="AU150" s="86"/>
+      <c r="AV150" s="86"/>
+      <c r="AW150" s="86"/>
+      <c r="AX150" s="86"/>
+      <c r="AY150" s="86"/>
+      <c r="AZ150" s="81"/>
       <c r="BA150" s="62"/>
       <c r="BB150" s="62"/>
-      <c r="BC150" s="80"/>
-      <c r="BD150" s="80"/>
-      <c r="BE150" s="80"/>
-      <c r="BF150" s="80"/>
-      <c r="BG150" s="80"/>
-      <c r="BH150" s="80"/>
-      <c r="BI150" s="80"/>
-      <c r="BJ150" s="80"/>
-      <c r="BK150" s="80"/>
-      <c r="BL150" s="80"/>
-      <c r="BM150" s="80"/>
-      <c r="BN150" s="80"/>
-      <c r="BO150" s="80"/>
-      <c r="BP150" s="80"/>
-      <c r="BQ150" s="80"/>
-      <c r="BR150" s="80"/>
-      <c r="BS150" s="80"/>
-      <c r="BT150" s="80"/>
-      <c r="BU150" s="80"/>
-      <c r="BV150" s="80"/>
-      <c r="BW150" s="80"/>
-      <c r="BX150" s="80"/>
-      <c r="BY150" s="80"/>
-      <c r="BZ150" s="80"/>
-      <c r="CA150" s="80"/>
-      <c r="CB150" s="80"/>
-      <c r="CC150" s="80"/>
-      <c r="CD150" s="80"/>
-      <c r="CE150" s="80"/>
-      <c r="CF150" s="80"/>
-      <c r="CG150" s="80"/>
-      <c r="CH150" s="80"/>
-      <c r="CI150" s="80"/>
-      <c r="CJ150" s="80"/>
-      <c r="CK150" s="80"/>
-      <c r="CL150" s="80"/>
-      <c r="CM150" s="80"/>
-      <c r="CN150" s="80"/>
-      <c r="CO150" s="80"/>
-      <c r="CP150" s="80"/>
-      <c r="CQ150" s="80"/>
-      <c r="CR150" s="80"/>
-      <c r="CS150" s="80"/>
-      <c r="CT150" s="80"/>
-      <c r="CU150" s="80"/>
-      <c r="CV150" s="80"/>
-      <c r="CW150" s="80"/>
-      <c r="CX150" s="80"/>
-      <c r="CY150" s="80"/>
-      <c r="CZ150" s="80"/>
-      <c r="DA150" s="80"/>
-      <c r="DB150" s="80"/>
-      <c r="DC150" s="80"/>
-      <c r="DD150" s="80"/>
-      <c r="DE150" s="80"/>
-      <c r="DF150" s="80"/>
-      <c r="DG150" s="80"/>
-      <c r="DH150" s="80"/>
-      <c r="DI150" s="80"/>
-      <c r="DJ150" s="80"/>
-      <c r="DK150" s="80"/>
-      <c r="DL150" s="80"/>
-      <c r="DM150" s="80"/>
-      <c r="DN150" s="80"/>
-      <c r="DO150" s="80"/>
-      <c r="DP150" s="80"/>
-      <c r="DQ150" s="80"/>
-      <c r="DR150" s="80"/>
-      <c r="DS150" s="80"/>
-      <c r="DT150" s="80"/>
-      <c r="DU150" s="80"/>
-      <c r="DV150" s="80"/>
-      <c r="DW150" s="80"/>
-      <c r="DX150" s="80"/>
-      <c r="DY150" s="80"/>
-      <c r="DZ150" s="80"/>
-      <c r="EA150" s="80"/>
-      <c r="EB150" s="80"/>
-      <c r="EC150" s="80"/>
-      <c r="ED150" s="80"/>
-      <c r="EE150" s="80"/>
-      <c r="EF150" s="80"/>
-      <c r="EG150" s="80"/>
-      <c r="EH150" s="80"/>
-      <c r="EI150" s="80"/>
-      <c r="EJ150" s="80"/>
-      <c r="EK150" s="80"/>
-      <c r="EL150" s="80"/>
-      <c r="EM150" s="80"/>
-      <c r="EN150" s="80"/>
-      <c r="EO150" s="80"/>
-      <c r="EP150" s="80"/>
-      <c r="EQ150" s="80"/>
-      <c r="ER150" s="80"/>
+      <c r="BC150" s="81"/>
+      <c r="BD150" s="81"/>
+      <c r="BE150" s="81"/>
+      <c r="BF150" s="81"/>
+      <c r="BG150" s="81"/>
+      <c r="BH150" s="81"/>
+      <c r="BI150" s="81"/>
+      <c r="BJ150" s="81"/>
+      <c r="BK150" s="81"/>
+      <c r="BL150" s="81"/>
+      <c r="BM150" s="81"/>
+      <c r="BN150" s="81"/>
+      <c r="BO150" s="81"/>
+      <c r="BP150" s="81"/>
+      <c r="BQ150" s="81"/>
+      <c r="BR150" s="81"/>
+      <c r="BS150" s="81"/>
+      <c r="BT150" s="81"/>
+      <c r="BU150" s="81"/>
+      <c r="BV150" s="81"/>
+      <c r="BW150" s="81"/>
+      <c r="BX150" s="81"/>
+      <c r="BY150" s="81"/>
+      <c r="BZ150" s="81"/>
+      <c r="CA150" s="81"/>
+      <c r="CB150" s="81"/>
+      <c r="CC150" s="81"/>
+      <c r="CD150" s="81"/>
+      <c r="CE150" s="81"/>
+      <c r="CF150" s="81"/>
+      <c r="CG150" s="81"/>
+      <c r="CH150" s="81"/>
+      <c r="CI150" s="81"/>
+      <c r="CJ150" s="81"/>
+      <c r="CK150" s="81"/>
+      <c r="CL150" s="81"/>
+      <c r="CM150" s="81"/>
+      <c r="CN150" s="81"/>
+      <c r="CO150" s="81"/>
+      <c r="CP150" s="81"/>
+      <c r="CQ150" s="81"/>
+      <c r="CR150" s="81"/>
+      <c r="CS150" s="81"/>
+      <c r="CT150" s="81"/>
+      <c r="CU150" s="81"/>
+      <c r="CV150" s="81"/>
+      <c r="CW150" s="81"/>
+      <c r="CX150" s="81"/>
+      <c r="CY150" s="81"/>
+      <c r="CZ150" s="81"/>
+      <c r="DA150" s="81"/>
+      <c r="DB150" s="81"/>
+      <c r="DC150" s="81"/>
+      <c r="DD150" s="81"/>
+      <c r="DE150" s="81"/>
+      <c r="DF150" s="81"/>
+      <c r="DG150" s="81"/>
+      <c r="DH150" s="81"/>
+      <c r="DI150" s="81"/>
+      <c r="DJ150" s="81"/>
+      <c r="DK150" s="81"/>
+      <c r="DL150" s="81"/>
+      <c r="DM150" s="81"/>
+      <c r="DN150" s="81"/>
+      <c r="DO150" s="81"/>
+      <c r="DP150" s="81"/>
+      <c r="DQ150" s="81"/>
+      <c r="DR150" s="81"/>
+      <c r="DS150" s="81"/>
+      <c r="DT150" s="81"/>
+      <c r="DU150" s="81"/>
+      <c r="DV150" s="81"/>
+      <c r="DW150" s="81"/>
+      <c r="DX150" s="81"/>
+      <c r="DY150" s="81"/>
+      <c r="DZ150" s="81"/>
+      <c r="EA150" s="81"/>
+      <c r="EB150" s="81"/>
+      <c r="EC150" s="81"/>
+      <c r="ED150" s="81"/>
+      <c r="EE150" s="81"/>
+      <c r="EF150" s="81"/>
+      <c r="EG150" s="81"/>
+      <c r="EH150" s="81"/>
+      <c r="EI150" s="81"/>
+      <c r="EJ150" s="81"/>
+      <c r="EK150" s="81"/>
+      <c r="EL150" s="81"/>
+      <c r="EM150" s="81"/>
+      <c r="EN150" s="81"/>
+      <c r="EO150" s="81"/>
+      <c r="EP150" s="81"/>
+      <c r="EQ150" s="81"/>
+      <c r="ER150" s="81"/>
     </row>
     <row r="151" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A151" s="58" t="s">
@@ -34742,39 +39003,39 @@
       </c>
       <c r="AQ151" s="58" t="n">
         <f aca="false">+AQ144/AQ52</f>
-        <v>0.47746180902041</v>
+        <v>0.531375504856742</v>
       </c>
       <c r="AR151" s="58" t="n">
         <f aca="false">+AR144/AR52</f>
-        <v>0.573057665493522</v>
+        <v>0.637992952417881</v>
       </c>
       <c r="AS151" s="58" t="n">
         <f aca="false">+AS144/AS52</f>
-        <v>0.394910581857692</v>
+        <v>0.464495740690375</v>
       </c>
       <c r="AT151" s="58" t="n">
         <f aca="false">+AT144/AT52</f>
-        <v>0.358950981451122</v>
+        <v>0.424486962631229</v>
       </c>
       <c r="AU151" s="58" t="n">
         <f aca="false">+AU144/AU52</f>
-        <v>0.356222964515213</v>
+        <v>0.413309661857599</v>
       </c>
       <c r="AV151" s="58" t="n">
         <f aca="false">+AV144/AV52</f>
-        <v>0.33709233319515</v>
+        <v>0.402872918918343</v>
       </c>
       <c r="AW151" s="58" t="n">
         <f aca="false">+AW144/AW52</f>
-        <v>0.334920426871128</v>
+        <v>0.400440096135653</v>
       </c>
       <c r="AX151" s="58" t="n">
         <f aca="false">+AX144/AX52</f>
-        <v>0.33297807554655</v>
+        <v>0.398262727338806</v>
       </c>
       <c r="AY151" s="58" t="n">
         <f aca="false">+AY144/AY52</f>
-        <v>0.331238884082536</v>
+        <v>0.345232413122455</v>
       </c>
       <c r="AZ151" s="39"/>
       <c r="BA151" s="56"/>
@@ -35965,42 +40226,42 @@
         <f aca="false">+(AVERAGE(AM101:AN101)/AN30)*365</f>
         <v>33.3849880079217</v>
       </c>
-      <c r="AO161" s="81" t="n">
+      <c r="AO161" s="82" t="n">
         <v>34</v>
       </c>
-      <c r="AP161" s="81" t="n">
+      <c r="AP161" s="82" t="n">
         <f aca="false">+AO161-1</f>
         <v>33</v>
       </c>
-      <c r="AQ161" s="81" t="n">
+      <c r="AQ161" s="82" t="n">
         <v>33</v>
       </c>
-      <c r="AR161" s="81" t="n">
+      <c r="AR161" s="82" t="n">
         <f aca="false">+AQ161-1</f>
         <v>32</v>
       </c>
-      <c r="AS161" s="81" t="n">
+      <c r="AS161" s="82" t="n">
         <v>32</v>
       </c>
-      <c r="AT161" s="81" t="n">
+      <c r="AT161" s="82" t="n">
         <f aca="false">+AS161-1</f>
         <v>31</v>
       </c>
-      <c r="AU161" s="81" t="n">
+      <c r="AU161" s="82" t="n">
         <v>31</v>
       </c>
-      <c r="AV161" s="81" t="n">
+      <c r="AV161" s="82" t="n">
         <f aca="false">+AU161-1</f>
         <v>30</v>
       </c>
-      <c r="AW161" s="81" t="n">
+      <c r="AW161" s="82" t="n">
         <v>30</v>
       </c>
-      <c r="AX161" s="81" t="n">
+      <c r="AX161" s="82" t="n">
         <f aca="false">+AW161-1</f>
         <v>29</v>
       </c>
-      <c r="AY161" s="81" t="n">
+      <c r="AY161" s="82" t="n">
         <v>29</v>
       </c>
     </row>
@@ -36136,47 +40397,47 @@
         <f aca="false">+(((AM111+AN111)/2)/AN32)*365</f>
         <v>83.6498272287491</v>
       </c>
-      <c r="AO162" s="81" t="n">
+      <c r="AO162" s="82" t="n">
         <f aca="false">+AN162+2</f>
         <v>85.6498272287491</v>
       </c>
-      <c r="AP162" s="81" t="n">
+      <c r="AP162" s="82" t="n">
         <f aca="false">+AO162+2</f>
         <v>87.6498272287491</v>
       </c>
-      <c r="AQ162" s="81" t="n">
+      <c r="AQ162" s="82" t="n">
         <f aca="false">+AP162+2</f>
         <v>89.6498272287491</v>
       </c>
-      <c r="AR162" s="81" t="n">
+      <c r="AR162" s="82" t="n">
         <f aca="false">+AQ162+2</f>
         <v>91.6498272287491</v>
       </c>
-      <c r="AS162" s="81" t="n">
+      <c r="AS162" s="82" t="n">
         <f aca="false">+AR162+2</f>
         <v>93.6498272287491</v>
       </c>
-      <c r="AT162" s="81" t="n">
+      <c r="AT162" s="82" t="n">
         <f aca="false">+AS162+2</f>
         <v>95.6498272287491</v>
       </c>
-      <c r="AU162" s="81" t="n">
+      <c r="AU162" s="82" t="n">
         <f aca="false">+AT162+2</f>
         <v>97.6498272287491</v>
       </c>
-      <c r="AV162" s="81" t="n">
+      <c r="AV162" s="82" t="n">
         <f aca="false">+AU162+2</f>
         <v>99.6498272287491</v>
       </c>
-      <c r="AW162" s="81" t="n">
+      <c r="AW162" s="82" t="n">
         <f aca="false">+AV162+2</f>
         <v>101.649827228749</v>
       </c>
-      <c r="AX162" s="81" t="n">
+      <c r="AX162" s="82" t="n">
         <f aca="false">+AW162+2</f>
         <v>103.649827228749</v>
       </c>
-      <c r="AY162" s="81" t="n">
+      <c r="AY162" s="82" t="n">
         <f aca="false">+AX162+2</f>
         <v>105.649827228749</v>
       </c>
@@ -36313,47 +40574,47 @@
         <f aca="false">+AN161-AN162</f>
         <v>-50.2648392208274</v>
       </c>
-      <c r="AO163" s="81" t="n">
+      <c r="AO163" s="82" t="n">
         <f aca="false">+AO161-AO162</f>
         <v>-51.6498272287491</v>
       </c>
-      <c r="AP163" s="81" t="n">
+      <c r="AP163" s="82" t="n">
         <f aca="false">+AP161-AP162</f>
         <v>-54.6498272287491</v>
       </c>
-      <c r="AQ163" s="81" t="n">
+      <c r="AQ163" s="82" t="n">
         <f aca="false">+AQ161-AQ162</f>
         <v>-56.6498272287491</v>
       </c>
-      <c r="AR163" s="81" t="n">
+      <c r="AR163" s="82" t="n">
         <f aca="false">+AR161-AR162</f>
         <v>-59.6498272287491</v>
       </c>
-      <c r="AS163" s="81" t="n">
+      <c r="AS163" s="82" t="n">
         <f aca="false">+AS161-AS162</f>
         <v>-61.6498272287491</v>
       </c>
-      <c r="AT163" s="81" t="n">
+      <c r="AT163" s="82" t="n">
         <f aca="false">+AT161-AT162</f>
         <v>-64.6498272287491</v>
       </c>
-      <c r="AU163" s="81" t="n">
+      <c r="AU163" s="82" t="n">
         <f aca="false">+AU161-AU162</f>
         <v>-66.6498272287491</v>
       </c>
-      <c r="AV163" s="81" t="n">
+      <c r="AV163" s="82" t="n">
         <f aca="false">+AV161-AV162</f>
         <v>-69.6498272287491</v>
       </c>
-      <c r="AW163" s="81" t="n">
+      <c r="AW163" s="82" t="n">
         <f aca="false">+AW161-AW162</f>
         <v>-71.649827228749</v>
       </c>
-      <c r="AX163" s="81" t="n">
+      <c r="AX163" s="82" t="n">
         <f aca="false">+AX161-AX162</f>
         <v>-74.649827228749</v>
       </c>
-      <c r="AY163" s="81" t="n">
+      <c r="AY163" s="82" t="n">
         <f aca="false">+AY161-AY162</f>
         <v>-76.649827228749</v>
       </c>
@@ -36367,25 +40628,25 @@
       <c r="A167" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="AH167" s="86" t="s">
+      <c r="AH167" s="87" t="s">
         <v>256</v>
       </c>
-      <c r="AI167" s="86" t="s">
+      <c r="AI167" s="87" t="s">
         <v>256</v>
       </c>
-      <c r="AJ167" s="86" t="n">
+      <c r="AJ167" s="87" t="n">
         <v>4</v>
       </c>
-      <c r="AK167" s="86" t="s">
+      <c r="AK167" s="87" t="s">
         <v>257</v>
       </c>
-      <c r="AL167" s="86" t="s">
+      <c r="AL167" s="87" t="s">
         <v>257</v>
       </c>
-      <c r="AM167" s="86" t="s">
+      <c r="AM167" s="87" t="s">
         <v>257</v>
       </c>
-      <c r="AN167" s="86" t="s">
+      <c r="AN167" s="87" t="s">
         <v>258</v>
       </c>
     </row>
@@ -36393,25 +40654,25 @@
       <c r="A168" s="3" t="s">
         <v>259</v>
       </c>
-      <c r="AH168" s="86" t="s">
+      <c r="AH168" s="87" t="s">
         <v>256</v>
       </c>
-      <c r="AI168" s="86" t="s">
+      <c r="AI168" s="87" t="s">
         <v>260</v>
       </c>
-      <c r="AJ168" s="86" t="s">
+      <c r="AJ168" s="87" t="s">
         <v>261</v>
       </c>
-      <c r="AK168" s="86" t="s">
+      <c r="AK168" s="87" t="s">
         <v>261</v>
       </c>
-      <c r="AL168" s="86" t="s">
+      <c r="AL168" s="87" t="s">
         <v>261</v>
       </c>
-      <c r="AM168" s="86" t="s">
+      <c r="AM168" s="87" t="s">
         <v>261</v>
       </c>
-      <c r="AN168" s="86" t="s">
+      <c r="AN168" s="87" t="s">
         <v>262</v>
       </c>
     </row>
@@ -36419,25 +40680,25 @@
       <c r="A169" s="3" t="s">
         <v>263</v>
       </c>
-      <c r="AH169" s="86" t="s">
+      <c r="AH169" s="87" t="s">
         <v>264</v>
       </c>
-      <c r="AI169" s="86" t="s">
+      <c r="AI169" s="87" t="s">
         <v>264</v>
       </c>
-      <c r="AJ169" s="86" t="s">
+      <c r="AJ169" s="87" t="s">
         <v>265</v>
       </c>
-      <c r="AK169" s="86" t="s">
+      <c r="AK169" s="87" t="s">
         <v>265</v>
       </c>
-      <c r="AL169" s="86" t="s">
+      <c r="AL169" s="87" t="s">
         <v>265</v>
       </c>
-      <c r="AM169" s="86" t="s">
+      <c r="AM169" s="87" t="s">
         <v>265</v>
       </c>
-      <c r="AN169" s="86" t="s">
+      <c r="AN169" s="87" t="s">
         <v>265</v>
       </c>
     </row>
@@ -36445,25 +40706,25 @@
       <c r="A170" s="3" t="s">
         <v>266</v>
       </c>
-      <c r="AH170" s="86" t="s">
+      <c r="AH170" s="87" t="s">
         <v>256</v>
       </c>
-      <c r="AI170" s="86" t="s">
+      <c r="AI170" s="87" t="s">
         <v>256</v>
       </c>
-      <c r="AJ170" s="86" t="s">
+      <c r="AJ170" s="87" t="s">
         <v>267</v>
       </c>
-      <c r="AK170" s="86" t="s">
+      <c r="AK170" s="87" t="s">
         <v>267</v>
       </c>
-      <c r="AL170" s="86" t="s">
+      <c r="AL170" s="87" t="s">
         <v>267</v>
       </c>
-      <c r="AM170" s="86" t="s">
+      <c r="AM170" s="87" t="s">
         <v>267</v>
       </c>
-      <c r="AN170" s="86" t="s">
+      <c r="AN170" s="87" t="s">
         <v>267</v>
       </c>
     </row>
@@ -37403,14 +41664,14 @@
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11.53"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="15.97"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="87" width="8.81"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="88" width="8.81"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="12.2"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="15.08"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="6" style="1" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="88" t="s">
+      <c r="A1" s="89" t="s">
         <v>96</v>
       </c>
     </row>
@@ -37418,7 +41679,7 @@
       <c r="B3" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="C3" s="89" t="s">
+      <c r="C3" s="90" t="s">
         <v>272</v>
       </c>
       <c r="D3" s="1" t="s">
@@ -37441,7 +41702,7 @@
       <c r="B4" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="C4" s="89" t="n">
+      <c r="C4" s="90" t="n">
         <v>3.5</v>
       </c>
       <c r="D4" s="1" t="s">
@@ -37461,7 +41722,7 @@
       <c r="B5" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="C5" s="89" t="n">
+      <c r="C5" s="90" t="n">
         <v>3.5</v>
       </c>
       <c r="D5" s="1" t="s">
@@ -37481,7 +41742,7 @@
       <c r="B6" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="C6" s="89" t="n">
+      <c r="C6" s="90" t="n">
         <v>3.5</v>
       </c>
       <c r="D6" s="1" t="s">
@@ -37501,7 +41762,7 @@
       <c r="B7" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="C7" s="89" t="n">
+      <c r="C7" s="90" t="n">
         <v>4.6</v>
       </c>
       <c r="D7" s="1" t="s">
@@ -37521,7 +41782,7 @@
       <c r="B8" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="C8" s="89" t="n">
+      <c r="C8" s="90" t="n">
         <v>4.3</v>
       </c>
       <c r="D8" s="1" t="s">
@@ -37541,7 +41802,7 @@
       <c r="B9" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="C9" s="89" t="n">
+      <c r="C9" s="90" t="n">
         <v>4.8</v>
       </c>
       <c r="D9" s="1" t="s">
@@ -37561,7 +41822,7 @@
       <c r="B10" s="1" t="s">
         <v>291</v>
       </c>
-      <c r="C10" s="89" t="n">
+      <c r="C10" s="90" t="n">
         <v>4.2</v>
       </c>
       <c r="D10" s="1" t="s">
@@ -37581,7 +41842,7 @@
       <c r="B11" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="C11" s="89" t="n">
+      <c r="C11" s="90" t="n">
         <v>4.55</v>
       </c>
       <c r="D11" s="1" t="s">
@@ -37601,7 +41862,7 @@
       <c r="B12" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="C12" s="89" t="n">
+      <c r="C12" s="90" t="n">
         <v>3.85</v>
       </c>
       <c r="D12" s="1" t="s">
@@ -37621,7 +41882,7 @@
       <c r="B13" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="C13" s="89" t="n">
+      <c r="C13" s="90" t="n">
         <v>3.85</v>
       </c>
       <c r="D13" s="1" t="s">
@@ -37641,7 +41902,7 @@
       <c r="B14" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="C14" s="89" t="n">
+      <c r="C14" s="90" t="n">
         <v>3.85</v>
       </c>
       <c r="D14" s="1" t="s">
@@ -37661,7 +41922,7 @@
       <c r="B15" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="C15" s="89" t="n">
+      <c r="C15" s="90" t="n">
         <v>4.6</v>
       </c>
       <c r="D15" s="1" t="s">
@@ -37681,7 +41942,7 @@
       <c r="B16" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="C16" s="89" t="n">
+      <c r="C16" s="90" t="n">
         <v>4.95</v>
       </c>
       <c r="D16" s="1" t="s">
@@ -37701,7 +41962,7 @@
       <c r="B17" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="C17" s="89" t="n">
+      <c r="C17" s="90" t="n">
         <v>4.75</v>
       </c>
       <c r="D17" s="1" t="s">
@@ -37721,7 +41982,7 @@
       <c r="B18" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="C18" s="89" t="n">
+      <c r="C18" s="90" t="n">
         <v>4.875</v>
       </c>
       <c r="D18" s="1" t="s">
@@ -37741,7 +42002,7 @@
       <c r="B19" s="1" t="s">
         <v>307</v>
       </c>
-      <c r="C19" s="89" t="n">
+      <c r="C19" s="90" t="n">
         <v>5.5</v>
       </c>
       <c r="D19" s="1" t="s">
@@ -37761,7 +42022,7 @@
       <c r="B20" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="C20" s="89" t="n">
+      <c r="C20" s="90" t="n">
         <v>4.45</v>
       </c>
       <c r="D20" s="1" t="s">
@@ -37781,7 +42042,7 @@
       <c r="B21" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="C21" s="89" t="n">
+      <c r="C21" s="90" t="n">
         <v>4.45</v>
       </c>
       <c r="D21" s="1" t="s">
@@ -37801,7 +42062,7 @@
       <c r="B22" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="C22" s="89" t="n">
+      <c r="C22" s="90" t="n">
         <v>4.45</v>
       </c>
       <c r="D22" s="1" t="s">
@@ -37821,7 +42082,7 @@
       <c r="B23" s="1" t="s">
         <v>313</v>
       </c>
-      <c r="C23" s="89" t="n">
+      <c r="C23" s="90" t="n">
         <v>5.6</v>
       </c>
       <c r="D23" s="1" t="s">
@@ -37841,7 +42102,7 @@
       <c r="B24" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="C24" s="89" t="n">
+      <c r="C24" s="90" t="n">
         <v>5.4</v>
       </c>
       <c r="D24" s="1" t="s">
@@ -37861,7 +42122,7 @@
       <c r="B25" s="1" t="s">
         <v>317</v>
       </c>
-      <c r="C25" s="89" t="n">
+      <c r="C25" s="90" t="n">
         <v>5.625</v>
       </c>
       <c r="D25" s="1" t="s">
@@ -37881,7 +42142,7 @@
       <c r="B26" s="1" t="s">
         <v>319</v>
       </c>
-      <c r="C26" s="89" t="n">
+      <c r="C26" s="90" t="n">
         <v>4.65</v>
       </c>
       <c r="D26" s="1" t="s">
@@ -37901,7 +42162,7 @@
       <c r="B27" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="C27" s="89" t="n">
+      <c r="C27" s="90" t="n">
         <v>4.65</v>
       </c>
       <c r="D27" s="1" t="s">
@@ -37921,7 +42182,7 @@
       <c r="B28" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="C28" s="89" t="n">
+      <c r="C28" s="90" t="n">
         <v>4.65</v>
       </c>
       <c r="D28" s="1" t="s">
@@ -37941,7 +42202,7 @@
       <c r="B29" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="C29" s="89" t="n">
+      <c r="C29" s="90" t="n">
         <v>5.75</v>
       </c>
       <c r="D29" s="1" t="s">
@@ -37961,7 +42222,7 @@
       <c r="B30" s="1" t="s">
         <v>325</v>
       </c>
-      <c r="C30" s="89" t="n">
+      <c r="C30" s="90" t="n">
         <v>5.55</v>
       </c>
       <c r="D30" s="1" t="s">
@@ -37981,7 +42242,7 @@
       <c r="B31" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="C31" s="89" t="n">
+      <c r="C31" s="90" t="n">
         <v>5.75</v>
       </c>
       <c r="D31" s="1" t="s">
@@ -38001,23 +42262,23 @@
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B32" s="90"/>
-      <c r="C32" s="91" t="n">
+      <c r="B32" s="91"/>
+      <c r="C32" s="92" t="n">
         <f aca="false">+AVERAGE(C4:C31)</f>
         <v>4.64821428571429</v>
       </c>
-      <c r="D32" s="90"/>
-      <c r="E32" s="90"/>
-      <c r="F32" s="90"/>
-      <c r="G32" s="90"/>
+      <c r="D32" s="91"/>
+      <c r="E32" s="91"/>
+      <c r="F32" s="91"/>
+      <c r="G32" s="91"/>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B33" s="90"/>
-      <c r="C33" s="91"/>
-      <c r="D33" s="90"/>
-      <c r="E33" s="90"/>
-      <c r="F33" s="90"/>
-      <c r="G33" s="90"/>
+      <c r="B33" s="91"/>
+      <c r="C33" s="92"/>
+      <c r="D33" s="91"/>
+      <c r="E33" s="91"/>
+      <c r="F33" s="91"/>
+      <c r="G33" s="91"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -38046,7 +42307,7 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="88" t="s">
+      <c r="A1" s="89" t="s">
         <v>96</v>
       </c>
     </row>
